--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,6 +2685,8168 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127412246</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>659647</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7189793</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127412260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>659617</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7189732</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127412274</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>659657</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7189693</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127412319</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>659459</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7189700</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127412282</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>659532</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7189692</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127412277</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>659674</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7189662</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127412292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>659492</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7189757</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127412256</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>659665</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7189754</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127412258</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>659663</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7189743</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127412249</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>659615</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7189777</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127412305</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>659567</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7189783</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127412309</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90361</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>659555</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7189806</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127412247</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>659638</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7189791</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127412295</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>659512</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7189786</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127412255</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>659629</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7189751</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127412290</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>659545</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7189763</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127412300</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>659617</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7189798</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127412288</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>659455</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7189725</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127412294</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>659520</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7189812</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127412306</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92604</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>149</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallgråticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>659582</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7189797</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127412297</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>659438</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7189796</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127412239</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>353</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>659675</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7189819</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127412261</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>659600</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7189733</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127412278</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>659622</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7189650</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127412315</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90361</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>659538</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7189669</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127412301</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>659617</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7189798</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127412271</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>659620</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7189703</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127412259</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>659620</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7189736</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127412251</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>659673</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7189773</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127412298</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>659428</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7189801</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127412269</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>659696</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7189717</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127412273</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>659657</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7189693</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127412250</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>659644</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7189774</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127412291</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>659545</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7189763</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127412293</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>659520</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7189812</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127412243</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>659677</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7189813</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127412241</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>659677</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7189813</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127412304</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>659596</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7189785</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127412280</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>659557</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7189710</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127412268</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>659696</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7189717</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127412318</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>659479</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7189697</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127412279</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>659576</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7189699</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127412272</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>659634</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7189692</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127412299</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>659637</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7189827</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127412317</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>659491</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7189693</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127412267</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>659676</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7189721</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127412265</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>659682</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7189733</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127412316</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>659527</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7189674</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127412245</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>659677</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7189799</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127412286</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>659491</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7189705</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127412312</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>659563</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7189659</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127412270</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>659696</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7189717</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127412252</v>
+      </c>
+      <c r="B72" t="n">
+        <v>90129</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>659674</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7189772</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127412262</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>659670</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7189732</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127412253</v>
+      </c>
+      <c r="B74" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>659620</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7189750</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127412285</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>659491</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7189705</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127412242</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>659677</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7189813</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127412254</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>659613</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7189750</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127412275</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>659650</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7189690</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127412244</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>659678</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7189811</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127412276</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>353</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>659721</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7189669</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127412289</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>659530</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7189750</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127412313</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>659548</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7189657</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127412296</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>659476</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7189791</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127412308</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>353</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>659555</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7189806</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127412284</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>659491</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7189705</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127412266</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92610</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>659689</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7189728</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127412283</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>659523</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7189683</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127412281</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>659533</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7189693</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127412307</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>659574</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7189797</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127412310</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>659559</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7189813</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127412287</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>659455</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7189725</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127412248</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>659638</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7189786</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127412240</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>659675</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7189819</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127412302</v>
+      </c>
+      <c r="B94" t="n">
+        <v>92608</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>659609</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7189804</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127412303</v>
+      </c>
+      <c r="B95" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>659596</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7189785</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127412257</v>
+      </c>
+      <c r="B96" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Mettjaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>659680</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7189752</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -3005,32 +3005,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412319</v>
+        <v>127412277</v>
       </c>
       <c r="B23" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659459</v>
+        <v>659674</v>
       </c>
       <c r="R23" t="n">
-        <v>7189700</v>
+        <v>7189662</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412277</v>
+        <v>127412319</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>92628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659674</v>
+        <v>659459</v>
       </c>
       <c r="R25" t="n">
-        <v>7189662</v>
+        <v>7189700</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412256</v>
+        <v>127412249</v>
       </c>
       <c r="B27" t="n">
         <v>92632</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>659665</v>
+        <v>659615</v>
       </c>
       <c r="R27" t="n">
-        <v>7189754</v>
+        <v>7189777</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412249</v>
+        <v>127412305</v>
       </c>
       <c r="B29" t="n">
         <v>92632</v>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659615</v>
+        <v>659567</v>
       </c>
       <c r="R29" t="n">
-        <v>7189777</v>
+        <v>7189783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>90361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R30" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412309</v>
+        <v>127412256</v>
       </c>
       <c r="B31" t="n">
-        <v>90361</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659555</v>
+        <v>659665</v>
       </c>
       <c r="R31" t="n">
-        <v>7189806</v>
+        <v>7189754</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412247</v>
+        <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>90129</v>
+        <v>92628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659638</v>
+        <v>659629</v>
       </c>
       <c r="R32" t="n">
-        <v>7189791</v>
+        <v>7189751</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412295</v>
+        <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>90129</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659512</v>
+        <v>659638</v>
       </c>
       <c r="R33" t="n">
-        <v>7189786</v>
+        <v>7189791</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412255</v>
+        <v>127412295</v>
       </c>
       <c r="B34" t="n">
-        <v>92628</v>
+        <v>78772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659629</v>
+        <v>659512</v>
       </c>
       <c r="R34" t="n">
-        <v>7189751</v>
+        <v>7189786</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>92628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R38" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>92628</v>
+        <v>78772</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R40" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,32 +4913,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412239</v>
+        <v>127412259</v>
       </c>
       <c r="B41" t="n">
-        <v>78681</v>
+        <v>90129</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659675</v>
+        <v>659620</v>
       </c>
       <c r="R41" t="n">
-        <v>7189819</v>
+        <v>7189736</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412261</v>
+        <v>127412315</v>
       </c>
       <c r="B42" t="n">
-        <v>92632</v>
+        <v>90361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659600</v>
+        <v>659538</v>
       </c>
       <c r="R42" t="n">
-        <v>7189733</v>
+        <v>7189669</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412278</v>
+        <v>127412271</v>
       </c>
       <c r="B43" t="n">
         <v>92632</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659622</v>
+        <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189650</v>
+        <v>7189703</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412315</v>
+        <v>127412301</v>
       </c>
       <c r="B44" t="n">
-        <v>90361</v>
+        <v>92608</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659538</v>
+        <v>659617</v>
       </c>
       <c r="R44" t="n">
-        <v>7189669</v>
+        <v>7189798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412301</v>
+        <v>127412261</v>
       </c>
       <c r="B45" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659617</v>
+        <v>659600</v>
       </c>
       <c r="R45" t="n">
-        <v>7189798</v>
+        <v>7189733</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412271</v>
+        <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92632</v>
+        <v>92610</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659620</v>
+        <v>659673</v>
       </c>
       <c r="R46" t="n">
-        <v>7189703</v>
+        <v>7189773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412259</v>
+        <v>127412278</v>
       </c>
       <c r="B47" t="n">
-        <v>90129</v>
+        <v>92632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659620</v>
+        <v>659622</v>
       </c>
       <c r="R47" t="n">
-        <v>7189736</v>
+        <v>7189650</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412251</v>
+        <v>127412239</v>
       </c>
       <c r="B48" t="n">
-        <v>92610</v>
+        <v>78681</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,21 +5666,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659673</v>
+        <v>659675</v>
       </c>
       <c r="R48" t="n">
-        <v>7189773</v>
+        <v>7189819</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412269</v>
+        <v>127412273</v>
       </c>
       <c r="B50" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>659696</v>
+        <v>659657</v>
       </c>
       <c r="R50" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412273</v>
+        <v>127412269</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>659657</v>
+        <v>659696</v>
       </c>
       <c r="R51" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412243</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>79632</v>
+        <v>92632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412241</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>78772</v>
+        <v>92608</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412304</v>
+        <v>127412279</v>
       </c>
       <c r="B57" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659596</v>
+        <v>659576</v>
       </c>
       <c r="R57" t="n">
-        <v>7189785</v>
+        <v>7189699</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412268</v>
+        <v>127412241</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412318</v>
+        <v>127412268</v>
       </c>
       <c r="B60" t="n">
-        <v>92632</v>
+        <v>79632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659479</v>
+        <v>659696</v>
       </c>
       <c r="R60" t="n">
-        <v>7189697</v>
+        <v>7189717</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412279</v>
+        <v>127412243</v>
       </c>
       <c r="B61" t="n">
-        <v>92632</v>
+        <v>79632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659576</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189699</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412317</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>92632</v>
+        <v>92610</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189693</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412267</v>
+        <v>127412312</v>
       </c>
       <c r="B65" t="n">
-        <v>79603</v>
+        <v>92610</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659676</v>
+        <v>659563</v>
       </c>
       <c r="R65" t="n">
-        <v>7189721</v>
+        <v>7189659</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B66" t="n">
         <v>92632</v>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R66" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412316</v>
+        <v>127412265</v>
       </c>
       <c r="B67" t="n">
         <v>92632</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659527</v>
+        <v>659682</v>
       </c>
       <c r="R67" t="n">
-        <v>7189674</v>
+        <v>7189733</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412245</v>
+        <v>127412317</v>
       </c>
       <c r="B68" t="n">
-        <v>92610</v>
+        <v>92632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R68" t="n">
-        <v>7189799</v>
+        <v>7189693</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412312</v>
+        <v>127412267</v>
       </c>
       <c r="B70" t="n">
-        <v>92610</v>
+        <v>79603</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659563</v>
+        <v>659676</v>
       </c>
       <c r="R70" t="n">
-        <v>7189659</v>
+        <v>7189721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B72" t="n">
-        <v>90129</v>
+        <v>78773</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R72" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412262</v>
+        <v>127412285</v>
       </c>
       <c r="B73" t="n">
-        <v>92632</v>
+        <v>78772</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659670</v>
+        <v>659491</v>
       </c>
       <c r="R73" t="n">
-        <v>7189732</v>
+        <v>7189705</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412262</v>
       </c>
       <c r="B75" t="n">
-        <v>78772</v>
+        <v>92632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659670</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189732</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412242</v>
+        <v>127412252</v>
       </c>
       <c r="B76" t="n">
-        <v>78773</v>
+        <v>90129</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659677</v>
+        <v>659674</v>
       </c>
       <c r="R76" t="n">
-        <v>7189813</v>
+        <v>7189772</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>92632</v>
+        <v>78681</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R77" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412244</v>
+        <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659678</v>
+        <v>659613</v>
       </c>
       <c r="R79" t="n">
-        <v>7189811</v>
+        <v>7189750</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412276</v>
+        <v>127412244</v>
       </c>
       <c r="B80" t="n">
-        <v>78681</v>
+        <v>92628</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659721</v>
+        <v>659678</v>
       </c>
       <c r="R80" t="n">
-        <v>7189669</v>
+        <v>7189811</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>78772</v>
+        <v>92608</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R81" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>92608</v>
+        <v>78772</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R82" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92610</v>
+        <v>78681</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412308</v>
+        <v>127412284</v>
       </c>
       <c r="B84" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659555</v>
+        <v>659491</v>
       </c>
       <c r="R84" t="n">
-        <v>7189806</v>
+        <v>7189705</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412284</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>92610</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659491</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189705</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,7 +9683,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B86" t="n">
         <v>92610</v>
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R86" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,7 +9789,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412283</v>
+        <v>127412287</v>
       </c>
       <c r="B87" t="n">
         <v>78772</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659523</v>
+        <v>659455</v>
       </c>
       <c r="R87" t="n">
-        <v>7189683</v>
+        <v>7189725</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B88" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R88" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412307</v>
+        <v>127412281</v>
       </c>
       <c r="B89" t="n">
-        <v>92608</v>
+        <v>78773</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +10012,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659574</v>
+        <v>659533</v>
       </c>
       <c r="R89" t="n">
-        <v>7189797</v>
+        <v>7189693</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412287</v>
+        <v>127412307</v>
       </c>
       <c r="B91" t="n">
-        <v>78772</v>
+        <v>92608</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659455</v>
+        <v>659574</v>
       </c>
       <c r="R91" t="n">
-        <v>7189725</v>
+        <v>7189797</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B92" t="n">
-        <v>92644</v>
+        <v>92620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R92" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,32 +10425,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412240</v>
+        <v>127412248</v>
       </c>
       <c r="B93" t="n">
-        <v>92620</v>
+        <v>92644</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659675</v>
+        <v>659638</v>
       </c>
       <c r="R93" t="n">
-        <v>7189819</v>
+        <v>7189786</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B95" t="n">
-        <v>92632</v>
+        <v>92608</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B96" t="n">
         <v>92632</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412246</v>
+        <v>127412274</v>
       </c>
       <c r="B20" t="n">
-        <v>90129</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659647</v>
+        <v>659657</v>
       </c>
       <c r="R20" t="n">
-        <v>7189793</v>
+        <v>7189693</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>92632</v>
+        <v>90129</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412274</v>
+        <v>127412260</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659657</v>
+        <v>659617</v>
       </c>
       <c r="R22" t="n">
-        <v>7189693</v>
+        <v>7189732</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412267</v>
       </c>
       <c r="B64" t="n">
-        <v>92610</v>
+        <v>79603</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659676</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189721</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412312</v>
+        <v>127412245</v>
       </c>
       <c r="B65" t="n">
         <v>92610</v>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659563</v>
+        <v>659677</v>
       </c>
       <c r="R65" t="n">
-        <v>7189659</v>
+        <v>7189799</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412316</v>
+        <v>127412312</v>
       </c>
       <c r="B66" t="n">
-        <v>92632</v>
+        <v>92610</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659527</v>
+        <v>659563</v>
       </c>
       <c r="R66" t="n">
-        <v>7189674</v>
+        <v>7189659</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B67" t="n">
         <v>92632</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R67" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412317</v>
+        <v>127412265</v>
       </c>
       <c r="B68" t="n">
         <v>92632</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659491</v>
+        <v>659682</v>
       </c>
       <c r="R68" t="n">
-        <v>7189693</v>
+        <v>7189733</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412286</v>
+        <v>127412317</v>
       </c>
       <c r="B69" t="n">
-        <v>79603</v>
+        <v>92632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7923,7 +7923,7 @@
         <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189705</v>
+        <v>7189693</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412267</v>
+        <v>127412270</v>
       </c>
       <c r="B70" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659676</v>
+        <v>659696</v>
       </c>
       <c r="R70" t="n">
-        <v>7189721</v>
+        <v>7189717</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412270</v>
+        <v>127412286</v>
       </c>
       <c r="B71" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R71" t="n">
-        <v>7189717</v>
+        <v>7189705</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412284</v>
+        <v>127412266</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>92610</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659491</v>
+        <v>659689</v>
       </c>
       <c r="R84" t="n">
-        <v>7189705</v>
+        <v>7189728</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B85" t="n">
         <v>92610</v>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412296</v>
+        <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>92610</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659476</v>
+        <v>659491</v>
       </c>
       <c r="R86" t="n">
-        <v>7189791</v>
+        <v>7189705</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>90129</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R20" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90129</v>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412260</v>
+        <v>127412274</v>
       </c>
       <c r="B22" t="n">
-        <v>92632</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659617</v>
+        <v>659657</v>
       </c>
       <c r="R22" t="n">
-        <v>7189732</v>
+        <v>7189693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412293</v>
+        <v>127412318</v>
       </c>
       <c r="B54" t="n">
-        <v>78773</v>
+        <v>92632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659520</v>
+        <v>659479</v>
       </c>
       <c r="R54" t="n">
-        <v>7189812</v>
+        <v>7189697</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B55" t="n">
-        <v>92632</v>
+        <v>92608</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412279</v>
       </c>
       <c r="B56" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659576</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189699</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92632</v>
+        <v>92608</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R57" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412280</v>
+        <v>127412268</v>
       </c>
       <c r="B58" t="n">
-        <v>92608</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659557</v>
+        <v>659696</v>
       </c>
       <c r="R58" t="n">
-        <v>7189710</v>
+        <v>7189717</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412268</v>
+        <v>127412243</v>
       </c>
       <c r="B60" t="n">
         <v>79632</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R60" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412243</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412242</v>
+        <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659677</v>
+        <v>659620</v>
       </c>
       <c r="R72" t="n">
-        <v>7189813</v>
+        <v>7189750</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412285</v>
+        <v>127412262</v>
       </c>
       <c r="B73" t="n">
-        <v>78772</v>
+        <v>92632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659491</v>
+        <v>659670</v>
       </c>
       <c r="R73" t="n">
-        <v>7189705</v>
+        <v>7189732</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412253</v>
+        <v>127412252</v>
       </c>
       <c r="B74" t="n">
-        <v>92616</v>
+        <v>90129</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659620</v>
+        <v>659674</v>
       </c>
       <c r="R74" t="n">
-        <v>7189750</v>
+        <v>7189772</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412262</v>
+        <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>92632</v>
+        <v>78772</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659670</v>
+        <v>659491</v>
       </c>
       <c r="R75" t="n">
-        <v>7189732</v>
+        <v>7189705</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>90129</v>
+        <v>78773</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R76" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412266</v>
+        <v>127412284</v>
       </c>
       <c r="B84" t="n">
-        <v>92610</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659689</v>
+        <v>659491</v>
       </c>
       <c r="R84" t="n">
-        <v>7189728</v>
+        <v>7189705</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412296</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
         <v>92610</v>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659476</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189791</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>92610</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R86" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>90129</v>
+        <v>92636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>92632</v>
+        <v>90133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>127412274</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412277</v>
+        <v>127412282</v>
       </c>
       <c r="B23" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659674</v>
+        <v>659532</v>
       </c>
       <c r="R23" t="n">
-        <v>7189662</v>
+        <v>7189692</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412282</v>
+        <v>127412277</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659532</v>
+        <v>659674</v>
       </c>
       <c r="R24" t="n">
-        <v>7189692</v>
+        <v>7189662</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92628</v>
+        <v>92614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R25" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92610</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R26" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412258</v>
+        <v>127412256</v>
       </c>
       <c r="B28" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659663</v>
+        <v>659665</v>
       </c>
       <c r="R28" t="n">
-        <v>7189743</v>
+        <v>7189754</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>92632</v>
+        <v>90365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R29" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412309</v>
+        <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>90361</v>
+        <v>92636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659555</v>
+        <v>659567</v>
       </c>
       <c r="R30" t="n">
-        <v>7189806</v>
+        <v>7189783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412256</v>
+        <v>127412258</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659665</v>
+        <v>659663</v>
       </c>
       <c r="R31" t="n">
-        <v>7189754</v>
+        <v>7189743</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3962,7 +3962,7 @@
         <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>90129</v>
+        <v>90133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127412295</v>
       </c>
       <c r="B34" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>127412297</v>
       </c>
       <c r="B38" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412306</v>
+        <v>127412294</v>
       </c>
       <c r="B39" t="n">
-        <v>92604</v>
+        <v>78776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>149</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659582</v>
+        <v>659520</v>
       </c>
       <c r="R39" t="n">
-        <v>7189797</v>
+        <v>7189812</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B40" t="n">
-        <v>78772</v>
+        <v>92608</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R40" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,32 +4913,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412259</v>
+        <v>127412251</v>
       </c>
       <c r="B41" t="n">
-        <v>90129</v>
+        <v>92614</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659620</v>
+        <v>659673</v>
       </c>
       <c r="R41" t="n">
-        <v>7189736</v>
+        <v>7189773</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412315</v>
+        <v>127412301</v>
       </c>
       <c r="B42" t="n">
-        <v>90361</v>
+        <v>92612</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659538</v>
+        <v>659617</v>
       </c>
       <c r="R42" t="n">
-        <v>7189669</v>
+        <v>7189798</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412271</v>
+        <v>127412261</v>
       </c>
       <c r="B43" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659620</v>
+        <v>659600</v>
       </c>
       <c r="R43" t="n">
-        <v>7189703</v>
+        <v>7189733</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412301</v>
+        <v>127412271</v>
       </c>
       <c r="B44" t="n">
-        <v>92608</v>
+        <v>92636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R44" t="n">
-        <v>7189798</v>
+        <v>7189703</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412261</v>
+        <v>127412278</v>
       </c>
       <c r="B45" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659600</v>
+        <v>659622</v>
       </c>
       <c r="R45" t="n">
-        <v>7189733</v>
+        <v>7189650</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412251</v>
+        <v>127412315</v>
       </c>
       <c r="B46" t="n">
-        <v>92610</v>
+        <v>90365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659673</v>
+        <v>659538</v>
       </c>
       <c r="R46" t="n">
-        <v>7189773</v>
+        <v>7189669</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412278</v>
+        <v>127412239</v>
       </c>
       <c r="B47" t="n">
-        <v>92632</v>
+        <v>78685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659622</v>
+        <v>659675</v>
       </c>
       <c r="R47" t="n">
-        <v>7189650</v>
+        <v>7189819</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412239</v>
+        <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>78681</v>
+        <v>90133</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659675</v>
+        <v>659620</v>
       </c>
       <c r="R48" t="n">
-        <v>7189819</v>
+        <v>7189736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>127412273</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>127412269</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B52" t="n">
-        <v>90129</v>
+        <v>90133</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R52" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B53" t="n">
-        <v>90129</v>
+        <v>90133</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R53" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412318</v>
+        <v>127412279</v>
       </c>
       <c r="B54" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659479</v>
+        <v>659576</v>
       </c>
       <c r="R54" t="n">
-        <v>7189697</v>
+        <v>7189699</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412304</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>92608</v>
+        <v>92636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659596</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189785</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412279</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>92632</v>
+        <v>92612</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659576</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189699</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6612,7 +6612,7 @@
         <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412268</v>
+        <v>127412241</v>
       </c>
       <c r="B58" t="n">
-        <v>79632</v>
+        <v>78776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412241</v>
+        <v>127412268</v>
       </c>
       <c r="B59" t="n">
-        <v>78772</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659696</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189717</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6930,7 +6930,7 @@
         <v>127412243</v>
       </c>
       <c r="B60" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>127412272</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>127412299</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412267</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>79603</v>
+        <v>92614</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659676</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189721</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412245</v>
+        <v>127412312</v>
       </c>
       <c r="B65" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659677</v>
+        <v>659563</v>
       </c>
       <c r="R65" t="n">
-        <v>7189799</v>
+        <v>7189659</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412312</v>
+        <v>127412317</v>
       </c>
       <c r="B66" t="n">
-        <v>92610</v>
+        <v>92636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659563</v>
+        <v>659491</v>
       </c>
       <c r="R66" t="n">
-        <v>7189659</v>
+        <v>7189693</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7672,7 +7672,7 @@
         <v>127412316</v>
       </c>
       <c r="B67" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>127412265</v>
       </c>
       <c r="B68" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412317</v>
+        <v>127412286</v>
       </c>
       <c r="B69" t="n">
-        <v>92632</v>
+        <v>79607</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7923,7 +7923,7 @@
         <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189693</v>
+        <v>7189705</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412270</v>
+        <v>127412267</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>79607</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659696</v>
+        <v>659676</v>
       </c>
       <c r="R70" t="n">
-        <v>7189717</v>
+        <v>7189721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412286</v>
+        <v>127412270</v>
       </c>
       <c r="B71" t="n">
-        <v>79603</v>
+        <v>78777</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R71" t="n">
-        <v>7189705</v>
+        <v>7189717</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412253</v>
+        <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>92616</v>
+        <v>92636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659620</v>
+        <v>659670</v>
       </c>
       <c r="R72" t="n">
-        <v>7189750</v>
+        <v>7189732</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412262</v>
+        <v>127412253</v>
       </c>
       <c r="B73" t="n">
-        <v>92632</v>
+        <v>92620</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659670</v>
+        <v>659620</v>
       </c>
       <c r="R73" t="n">
-        <v>7189732</v>
+        <v>7189750</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8414,7 +8414,7 @@
         <v>127412252</v>
       </c>
       <c r="B74" t="n">
-        <v>90129</v>
+        <v>90133</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412275</v>
+        <v>127412254</v>
       </c>
       <c r="B78" t="n">
-        <v>79632</v>
+        <v>92636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659650</v>
+        <v>659613</v>
       </c>
       <c r="R78" t="n">
-        <v>7189690</v>
+        <v>7189750</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412254</v>
+        <v>127412244</v>
       </c>
       <c r="B79" t="n">
         <v>92632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659613</v>
+        <v>659678</v>
       </c>
       <c r="R79" t="n">
-        <v>7189750</v>
+        <v>7189811</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412244</v>
+        <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>92628</v>
+        <v>79636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659678</v>
+        <v>659650</v>
       </c>
       <c r="R80" t="n">
-        <v>7189811</v>
+        <v>7189690</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
         <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>92614</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R84" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9580,7 +9580,7 @@
         <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412296</v>
+        <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>92610</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659476</v>
+        <v>659491</v>
       </c>
       <c r="R86" t="n">
-        <v>7189791</v>
+        <v>7189705</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412287</v>
+        <v>127412240</v>
       </c>
       <c r="B87" t="n">
-        <v>78772</v>
+        <v>92624</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659455</v>
+        <v>659675</v>
       </c>
       <c r="R87" t="n">
-        <v>7189725</v>
+        <v>7189819</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412283</v>
+        <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>78772</v>
+        <v>92612</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659523</v>
+        <v>659574</v>
       </c>
       <c r="R88" t="n">
-        <v>7189683</v>
+        <v>7189797</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412281</v>
+        <v>127412310</v>
       </c>
       <c r="B89" t="n">
-        <v>78773</v>
+        <v>92612</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +10012,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659533</v>
+        <v>659559</v>
       </c>
       <c r="R89" t="n">
-        <v>7189693</v>
+        <v>7189813</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412310</v>
+        <v>127412248</v>
       </c>
       <c r="B90" t="n">
-        <v>92608</v>
+        <v>92648</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659559</v>
+        <v>659638</v>
       </c>
       <c r="R90" t="n">
-        <v>7189813</v>
+        <v>7189786</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412307</v>
+        <v>127412287</v>
       </c>
       <c r="B91" t="n">
-        <v>92608</v>
+        <v>78776</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659574</v>
+        <v>659455</v>
       </c>
       <c r="R91" t="n">
-        <v>7189797</v>
+        <v>7189725</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412240</v>
+        <v>127412283</v>
       </c>
       <c r="B92" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659675</v>
+        <v>659523</v>
       </c>
       <c r="R92" t="n">
-        <v>7189819</v>
+        <v>7189683</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412248</v>
+        <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>92644</v>
+        <v>78777</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659638</v>
+        <v>659533</v>
       </c>
       <c r="R93" t="n">
-        <v>7189786</v>
+        <v>7189693</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B94" t="n">
-        <v>92632</v>
+        <v>92612</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R94" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92608</v>
+        <v>92636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B96" t="n">
-        <v>92632</v>
+        <v>92636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R96" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B20" t="n">
-        <v>92636</v>
+        <v>90133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R20" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90133</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412282</v>
+        <v>127412277</v>
       </c>
       <c r="B23" t="n">
         <v>92636</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659532</v>
+        <v>659674</v>
       </c>
       <c r="R23" t="n">
-        <v>7189692</v>
+        <v>7189662</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412277</v>
+        <v>127412282</v>
       </c>
       <c r="B24" t="n">
         <v>92636</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659674</v>
+        <v>659532</v>
       </c>
       <c r="R24" t="n">
-        <v>7189662</v>
+        <v>7189692</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B25" t="n">
-        <v>92614</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R25" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B26" t="n">
-        <v>92632</v>
+        <v>92614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R26" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412256</v>
+        <v>127412258</v>
       </c>
       <c r="B28" t="n">
         <v>92636</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659665</v>
+        <v>659663</v>
       </c>
       <c r="R28" t="n">
-        <v>7189754</v>
+        <v>7189743</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412309</v>
+        <v>127412305</v>
       </c>
       <c r="B29" t="n">
-        <v>90365</v>
+        <v>92636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659555</v>
+        <v>659567</v>
       </c>
       <c r="R29" t="n">
-        <v>7189806</v>
+        <v>7189783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B30" t="n">
-        <v>92636</v>
+        <v>90365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R30" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412258</v>
+        <v>127412256</v>
       </c>
       <c r="B31" t="n">
         <v>92636</v>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659663</v>
+        <v>659665</v>
       </c>
       <c r="R31" t="n">
-        <v>7189743</v>
+        <v>7189754</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412300</v>
+        <v>127412288</v>
       </c>
       <c r="B36" t="n">
-        <v>92636</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,21 +4394,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659617</v>
+        <v>659455</v>
       </c>
       <c r="R36" t="n">
-        <v>7189798</v>
+        <v>7189725</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412288</v>
+        <v>127412300</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659455</v>
+        <v>659617</v>
       </c>
       <c r="R37" t="n">
-        <v>7189725</v>
+        <v>7189798</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B38" t="n">
-        <v>92632</v>
+        <v>78776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R38" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>92632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412251</v>
+        <v>127412315</v>
       </c>
       <c r="B41" t="n">
-        <v>92614</v>
+        <v>90365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659673</v>
+        <v>659538</v>
       </c>
       <c r="R41" t="n">
-        <v>7189773</v>
+        <v>7189669</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412301</v>
+        <v>127412271</v>
       </c>
       <c r="B42" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R42" t="n">
-        <v>7189798</v>
+        <v>7189703</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412261</v>
+        <v>127412301</v>
       </c>
       <c r="B43" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659600</v>
+        <v>659617</v>
       </c>
       <c r="R43" t="n">
-        <v>7189733</v>
+        <v>7189798</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412271</v>
+        <v>127412261</v>
       </c>
       <c r="B44" t="n">
         <v>92636</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659620</v>
+        <v>659600</v>
       </c>
       <c r="R44" t="n">
-        <v>7189703</v>
+        <v>7189733</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412278</v>
+        <v>127412251</v>
       </c>
       <c r="B45" t="n">
-        <v>92636</v>
+        <v>92614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659622</v>
+        <v>659673</v>
       </c>
       <c r="R45" t="n">
-        <v>7189650</v>
+        <v>7189773</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412315</v>
+        <v>127412278</v>
       </c>
       <c r="B46" t="n">
-        <v>90365</v>
+        <v>92636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659538</v>
+        <v>659622</v>
       </c>
       <c r="R46" t="n">
-        <v>7189669</v>
+        <v>7189650</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412279</v>
+        <v>127412293</v>
       </c>
       <c r="B54" t="n">
-        <v>92636</v>
+        <v>78777</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659576</v>
+        <v>659520</v>
       </c>
       <c r="R54" t="n">
-        <v>7189699</v>
+        <v>7189812</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412241</v>
       </c>
       <c r="B55" t="n">
-        <v>92636</v>
+        <v>78776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659677</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189813</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412268</v>
       </c>
       <c r="B56" t="n">
-        <v>92612</v>
+        <v>79636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659696</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189717</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412280</v>
+        <v>127412243</v>
       </c>
       <c r="B57" t="n">
-        <v>92612</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659557</v>
+        <v>659677</v>
       </c>
       <c r="R57" t="n">
-        <v>7189710</v>
+        <v>7189813</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412241</v>
+        <v>127412318</v>
       </c>
       <c r="B58" t="n">
-        <v>78776</v>
+        <v>92636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412268</v>
+        <v>127412304</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>92612</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659696</v>
+        <v>659596</v>
       </c>
       <c r="R59" t="n">
-        <v>7189717</v>
+        <v>7189785</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412243</v>
+        <v>127412279</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659677</v>
+        <v>659576</v>
       </c>
       <c r="R60" t="n">
-        <v>7189813</v>
+        <v>7189699</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412280</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>92612</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659557</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189710</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412317</v>
+        <v>127412316</v>
       </c>
       <c r="B66" t="n">
         <v>92636</v>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659491</v>
+        <v>659527</v>
       </c>
       <c r="R66" t="n">
-        <v>7189693</v>
+        <v>7189674</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412316</v>
+        <v>127412265</v>
       </c>
       <c r="B67" t="n">
         <v>92636</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659527</v>
+        <v>659682</v>
       </c>
       <c r="R67" t="n">
-        <v>7189674</v>
+        <v>7189733</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412265</v>
+        <v>127412317</v>
       </c>
       <c r="B68" t="n">
         <v>92636</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659682</v>
+        <v>659491</v>
       </c>
       <c r="R68" t="n">
-        <v>7189733</v>
+        <v>7189693</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412262</v>
+        <v>127412252</v>
       </c>
       <c r="B72" t="n">
-        <v>92636</v>
+        <v>90133</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659670</v>
+        <v>659674</v>
       </c>
       <c r="R72" t="n">
-        <v>7189732</v>
+        <v>7189772</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412253</v>
+        <v>127412285</v>
       </c>
       <c r="B73" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659620</v>
+        <v>659491</v>
       </c>
       <c r="R73" t="n">
-        <v>7189750</v>
+        <v>7189705</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412252</v>
+        <v>127412253</v>
       </c>
       <c r="B74" t="n">
-        <v>90133</v>
+        <v>92620</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659674</v>
+        <v>659620</v>
       </c>
       <c r="R74" t="n">
-        <v>7189772</v>
+        <v>7189750</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412262</v>
       </c>
       <c r="B75" t="n">
-        <v>78776</v>
+        <v>92636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659670</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189732</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412276</v>
+        <v>127412275</v>
       </c>
       <c r="B77" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659721</v>
+        <v>659650</v>
       </c>
       <c r="R77" t="n">
-        <v>7189669</v>
+        <v>7189690</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412275</v>
+        <v>127412276</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659650</v>
+        <v>659721</v>
       </c>
       <c r="R80" t="n">
-        <v>7189690</v>
+        <v>7189669</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B81" t="n">
-        <v>92612</v>
+        <v>78776</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R81" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B82" t="n">
-        <v>78776</v>
+        <v>92612</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R82" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412296</v>
       </c>
       <c r="B83" t="n">
-        <v>78685</v>
+        <v>92614</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659476</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189791</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B84" t="n">
-        <v>92614</v>
+        <v>78685</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R84" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412284</v>
       </c>
       <c r="B85" t="n">
-        <v>92614</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659491</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189705</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412284</v>
+        <v>127412266</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>92614</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659491</v>
+        <v>659689</v>
       </c>
       <c r="R86" t="n">
-        <v>7189705</v>
+        <v>7189728</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412240</v>
+        <v>127412310</v>
       </c>
       <c r="B87" t="n">
-        <v>92624</v>
+        <v>92612</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659675</v>
+        <v>659559</v>
       </c>
       <c r="R87" t="n">
-        <v>7189819</v>
+        <v>7189813</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412310</v>
+        <v>127412240</v>
       </c>
       <c r="B89" t="n">
-        <v>92612</v>
+        <v>92624</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659559</v>
+        <v>659675</v>
       </c>
       <c r="R89" t="n">
-        <v>7189813</v>
+        <v>7189819</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412248</v>
+        <v>127412287</v>
       </c>
       <c r="B90" t="n">
-        <v>92648</v>
+        <v>78776</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659638</v>
+        <v>659455</v>
       </c>
       <c r="R90" t="n">
-        <v>7189786</v>
+        <v>7189725</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412287</v>
+        <v>127412248</v>
       </c>
       <c r="B91" t="n">
-        <v>78776</v>
+        <v>92648</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659455</v>
+        <v>659638</v>
       </c>
       <c r="R91" t="n">
-        <v>7189725</v>
+        <v>7189786</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -4913,32 +4913,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412315</v>
+        <v>127412259</v>
       </c>
       <c r="B41" t="n">
-        <v>90365</v>
+        <v>90133</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659538</v>
+        <v>659620</v>
       </c>
       <c r="R41" t="n">
-        <v>7189669</v>
+        <v>7189736</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412271</v>
+        <v>127412315</v>
       </c>
       <c r="B42" t="n">
-        <v>92636</v>
+        <v>90365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659620</v>
+        <v>659538</v>
       </c>
       <c r="R42" t="n">
-        <v>7189703</v>
+        <v>7189669</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412301</v>
+        <v>127412271</v>
       </c>
       <c r="B43" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189798</v>
+        <v>7189703</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412261</v>
+        <v>127412301</v>
       </c>
       <c r="B44" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659600</v>
+        <v>659617</v>
       </c>
       <c r="R44" t="n">
-        <v>7189733</v>
+        <v>7189798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412251</v>
+        <v>127412261</v>
       </c>
       <c r="B45" t="n">
-        <v>92614</v>
+        <v>92636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659673</v>
+        <v>659600</v>
       </c>
       <c r="R45" t="n">
-        <v>7189773</v>
+        <v>7189733</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412278</v>
+        <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92636</v>
+        <v>92614</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659622</v>
+        <v>659673</v>
       </c>
       <c r="R46" t="n">
-        <v>7189650</v>
+        <v>7189773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412239</v>
+        <v>127412278</v>
       </c>
       <c r="B47" t="n">
-        <v>78685</v>
+        <v>92636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659675</v>
+        <v>659622</v>
       </c>
       <c r="R47" t="n">
-        <v>7189819</v>
+        <v>7189650</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412259</v>
+        <v>127412239</v>
       </c>
       <c r="B48" t="n">
-        <v>90133</v>
+        <v>78685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659620</v>
+        <v>659675</v>
       </c>
       <c r="R48" t="n">
-        <v>7189736</v>
+        <v>7189819</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B95" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B96" t="n">
         <v>92636</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412293</v>
+        <v>127412241</v>
       </c>
       <c r="B54" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R54" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412241</v>
+        <v>127412268</v>
       </c>
       <c r="B55" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659677</v>
+        <v>659696</v>
       </c>
       <c r="R55" t="n">
-        <v>7189813</v>
+        <v>7189717</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412268</v>
+        <v>127412243</v>
       </c>
       <c r="B56" t="n">
         <v>79636</v>
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R56" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412243</v>
+        <v>127412318</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R57" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B58" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R58" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412304</v>
+        <v>127412279</v>
       </c>
       <c r="B59" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659596</v>
+        <v>659576</v>
       </c>
       <c r="R59" t="n">
-        <v>7189785</v>
+        <v>7189699</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B60" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R60" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412280</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>92612</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659557</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189710</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B94" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R94" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B96" t="n">
         <v>92636</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R96" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412246</v>
+        <v>127412274</v>
       </c>
       <c r="B20" t="n">
-        <v>90133</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659647</v>
+        <v>659657</v>
       </c>
       <c r="R20" t="n">
-        <v>7189793</v>
+        <v>7189693</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>90133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R22" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412288</v>
+        <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,21 +4394,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659455</v>
+        <v>659617</v>
       </c>
       <c r="R36" t="n">
-        <v>7189725</v>
+        <v>7189798</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412300</v>
+        <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>92636</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659617</v>
+        <v>659455</v>
       </c>
       <c r="R37" t="n">
-        <v>7189798</v>
+        <v>7189725</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>78776</v>
+        <v>92608</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R38" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412306</v>
+        <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>92608</v>
+        <v>78776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>149</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659582</v>
+        <v>659520</v>
       </c>
       <c r="R40" t="n">
-        <v>7189797</v>
+        <v>7189812</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,32 +4913,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412259</v>
+        <v>127412315</v>
       </c>
       <c r="B41" t="n">
-        <v>90133</v>
+        <v>90365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>1962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659620</v>
+        <v>659538</v>
       </c>
       <c r="R41" t="n">
-        <v>7189736</v>
+        <v>7189669</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412315</v>
+        <v>127412271</v>
       </c>
       <c r="B42" t="n">
-        <v>90365</v>
+        <v>92636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659538</v>
+        <v>659620</v>
       </c>
       <c r="R42" t="n">
-        <v>7189669</v>
+        <v>7189703</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412271</v>
+        <v>127412261</v>
       </c>
       <c r="B43" t="n">
         <v>92636</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659620</v>
+        <v>659600</v>
       </c>
       <c r="R43" t="n">
-        <v>7189703</v>
+        <v>7189733</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412301</v>
+        <v>127412278</v>
       </c>
       <c r="B44" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659617</v>
+        <v>659622</v>
       </c>
       <c r="R44" t="n">
-        <v>7189798</v>
+        <v>7189650</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412261</v>
+        <v>127412239</v>
       </c>
       <c r="B45" t="n">
-        <v>92636</v>
+        <v>78685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659600</v>
+        <v>659675</v>
       </c>
       <c r="R45" t="n">
-        <v>7189733</v>
+        <v>7189819</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412278</v>
+        <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659622</v>
+        <v>659617</v>
       </c>
       <c r="R47" t="n">
-        <v>7189650</v>
+        <v>7189798</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412239</v>
+        <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>78685</v>
+        <v>90133</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659675</v>
+        <v>659620</v>
       </c>
       <c r="R48" t="n">
-        <v>7189819</v>
+        <v>7189736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412273</v>
+        <v>127412269</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>659657</v>
+        <v>659696</v>
       </c>
       <c r="R50" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412269</v>
+        <v>127412273</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>659696</v>
+        <v>659657</v>
       </c>
       <c r="R51" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412241</v>
+        <v>127412318</v>
       </c>
       <c r="B54" t="n">
-        <v>78776</v>
+        <v>92636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R54" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412268</v>
+        <v>127412279</v>
       </c>
       <c r="B55" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659696</v>
+        <v>659576</v>
       </c>
       <c r="R55" t="n">
-        <v>7189717</v>
+        <v>7189699</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412243</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>92612</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412318</v>
+        <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659479</v>
+        <v>659557</v>
       </c>
       <c r="R57" t="n">
-        <v>7189697</v>
+        <v>7189710</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412304</v>
+        <v>127412268</v>
       </c>
       <c r="B58" t="n">
-        <v>92612</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659596</v>
+        <v>659696</v>
       </c>
       <c r="R58" t="n">
-        <v>7189785</v>
+        <v>7189717</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412279</v>
+        <v>127412243</v>
       </c>
       <c r="B59" t="n">
-        <v>92636</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659576</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189699</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412280</v>
+        <v>127412293</v>
       </c>
       <c r="B60" t="n">
-        <v>92612</v>
+        <v>78777</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659557</v>
+        <v>659520</v>
       </c>
       <c r="R60" t="n">
-        <v>7189710</v>
+        <v>7189812</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412241</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412272</v>
+        <v>127412299</v>
       </c>
       <c r="B62" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>659634</v>
+        <v>659637</v>
       </c>
       <c r="R62" t="n">
-        <v>7189692</v>
+        <v>7189827</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412299</v>
+        <v>127412272</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,21 +7256,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>659637</v>
+        <v>659634</v>
       </c>
       <c r="R63" t="n">
-        <v>7189827</v>
+        <v>7189692</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412286</v>
       </c>
       <c r="B64" t="n">
-        <v>92614</v>
+        <v>79607</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189705</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412312</v>
+        <v>127412267</v>
       </c>
       <c r="B65" t="n">
-        <v>92614</v>
+        <v>79607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659563</v>
+        <v>659676</v>
       </c>
       <c r="R65" t="n">
-        <v>7189659</v>
+        <v>7189721</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412316</v>
+        <v>127412270</v>
       </c>
       <c r="B66" t="n">
-        <v>92636</v>
+        <v>78777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659527</v>
+        <v>659696</v>
       </c>
       <c r="R66" t="n">
-        <v>7189674</v>
+        <v>7189717</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B67" t="n">
         <v>92636</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R67" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412317</v>
+        <v>127412265</v>
       </c>
       <c r="B68" t="n">
         <v>92636</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659491</v>
+        <v>659682</v>
       </c>
       <c r="R68" t="n">
-        <v>7189693</v>
+        <v>7189733</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412286</v>
+        <v>127412317</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>92636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7923,7 +7923,7 @@
         <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189705</v>
+        <v>7189693</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412267</v>
+        <v>127412245</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>92614</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659676</v>
+        <v>659677</v>
       </c>
       <c r="R70" t="n">
-        <v>7189721</v>
+        <v>7189799</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412270</v>
+        <v>127412312</v>
       </c>
       <c r="B71" t="n">
-        <v>78777</v>
+        <v>92614</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659696</v>
+        <v>659563</v>
       </c>
       <c r="R71" t="n">
-        <v>7189717</v>
+        <v>7189659</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412252</v>
+        <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>90133</v>
+        <v>92636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659674</v>
+        <v>659670</v>
       </c>
       <c r="R72" t="n">
-        <v>7189772</v>
+        <v>7189732</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412285</v>
+        <v>127412242</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R73" t="n">
-        <v>7189705</v>
+        <v>7189813</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412262</v>
+        <v>127412252</v>
       </c>
       <c r="B75" t="n">
-        <v>92636</v>
+        <v>90133</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659670</v>
+        <v>659674</v>
       </c>
       <c r="R75" t="n">
-        <v>7189732</v>
+        <v>7189772</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412242</v>
+        <v>127412285</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,21 +8634,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R76" t="n">
-        <v>7189813</v>
+        <v>7189705</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412275</v>
+        <v>127412254</v>
       </c>
       <c r="B77" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659650</v>
+        <v>659613</v>
       </c>
       <c r="R77" t="n">
-        <v>7189690</v>
+        <v>7189750</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B78" t="n">
-        <v>92636</v>
+        <v>78685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R78" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412276</v>
+        <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659721</v>
+        <v>659650</v>
       </c>
       <c r="R80" t="n">
-        <v>7189669</v>
+        <v>7189690</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>78776</v>
+        <v>92612</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R81" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>92612</v>
+        <v>78776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R82" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92614</v>
+        <v>78685</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412308</v>
+        <v>127412284</v>
       </c>
       <c r="B84" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659555</v>
+        <v>659491</v>
       </c>
       <c r="R84" t="n">
-        <v>7189806</v>
+        <v>7189705</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>92614</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R85" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412310</v>
+        <v>127412240</v>
       </c>
       <c r="B87" t="n">
-        <v>92612</v>
+        <v>92624</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659559</v>
+        <v>659675</v>
       </c>
       <c r="R87" t="n">
-        <v>7189813</v>
+        <v>7189819</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412307</v>
+        <v>127412248</v>
       </c>
       <c r="B88" t="n">
-        <v>92612</v>
+        <v>92648</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659574</v>
+        <v>659638</v>
       </c>
       <c r="R88" t="n">
-        <v>7189797</v>
+        <v>7189786</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412240</v>
+        <v>127412307</v>
       </c>
       <c r="B89" t="n">
-        <v>92624</v>
+        <v>92612</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659675</v>
+        <v>659574</v>
       </c>
       <c r="R89" t="n">
-        <v>7189819</v>
+        <v>7189797</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412287</v>
+        <v>127412310</v>
       </c>
       <c r="B90" t="n">
-        <v>78776</v>
+        <v>92612</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659455</v>
+        <v>659559</v>
       </c>
       <c r="R90" t="n">
-        <v>7189725</v>
+        <v>7189813</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412248</v>
+        <v>127412287</v>
       </c>
       <c r="B91" t="n">
-        <v>92648</v>
+        <v>78776</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659638</v>
+        <v>659455</v>
       </c>
       <c r="R91" t="n">
-        <v>7189786</v>
+        <v>7189725</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10637,7 +10637,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B95" t="n">
         <v>92636</v>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B96" t="n">
         <v>92636</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412274</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>92636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659657</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189693</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>92636</v>
+        <v>90133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412246</v>
+        <v>127412274</v>
       </c>
       <c r="B22" t="n">
-        <v>90133</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659647</v>
+        <v>659657</v>
       </c>
       <c r="R22" t="n">
-        <v>7189793</v>
+        <v>7189693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412255</v>
+        <v>127412247</v>
       </c>
       <c r="B32" t="n">
-        <v>92632</v>
+        <v>90133</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659629</v>
+        <v>659638</v>
       </c>
       <c r="R32" t="n">
-        <v>7189751</v>
+        <v>7189791</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412247</v>
+        <v>127412295</v>
       </c>
       <c r="B33" t="n">
-        <v>90133</v>
+        <v>78776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659638</v>
+        <v>659512</v>
       </c>
       <c r="R33" t="n">
-        <v>7189791</v>
+        <v>7189786</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412295</v>
+        <v>127412255</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>92632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659512</v>
+        <v>659629</v>
       </c>
       <c r="R34" t="n">
-        <v>7189786</v>
+        <v>7189751</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B38" t="n">
-        <v>92608</v>
+        <v>92632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R38" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412306</v>
       </c>
       <c r="B39" t="n">
-        <v>92632</v>
+        <v>92608</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659582</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189797</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B54" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R54" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B55" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R55" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412241</v>
       </c>
       <c r="B56" t="n">
-        <v>92612</v>
+        <v>78776</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659677</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189813</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412280</v>
+        <v>127412268</v>
       </c>
       <c r="B57" t="n">
-        <v>92612</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659557</v>
+        <v>659696</v>
       </c>
       <c r="R57" t="n">
-        <v>7189710</v>
+        <v>7189717</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412268</v>
+        <v>127412243</v>
       </c>
       <c r="B58" t="n">
         <v>79636</v>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412243</v>
+        <v>127412318</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>92636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412293</v>
+        <v>127412279</v>
       </c>
       <c r="B60" t="n">
-        <v>78777</v>
+        <v>92636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659520</v>
+        <v>659576</v>
       </c>
       <c r="R60" t="n">
-        <v>7189812</v>
+        <v>7189699</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412241</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412262</v>
+        <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>92636</v>
+        <v>92620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659670</v>
+        <v>659620</v>
       </c>
       <c r="R72" t="n">
-        <v>7189732</v>
+        <v>7189750</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412242</v>
+        <v>127412252</v>
       </c>
       <c r="B73" t="n">
-        <v>78777</v>
+        <v>90133</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659677</v>
+        <v>659674</v>
       </c>
       <c r="R73" t="n">
-        <v>7189813</v>
+        <v>7189772</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412253</v>
+        <v>127412285</v>
       </c>
       <c r="B74" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659620</v>
+        <v>659491</v>
       </c>
       <c r="R74" t="n">
-        <v>7189750</v>
+        <v>7189705</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412252</v>
+        <v>127412262</v>
       </c>
       <c r="B75" t="n">
-        <v>90133</v>
+        <v>92636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659674</v>
+        <v>659670</v>
       </c>
       <c r="R75" t="n">
-        <v>7189772</v>
+        <v>7189732</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412285</v>
+        <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,21 +8634,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R76" t="n">
-        <v>7189705</v>
+        <v>7189813</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8835,32 +8835,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412276</v>
+        <v>127412244</v>
       </c>
       <c r="B78" t="n">
-        <v>78685</v>
+        <v>92632</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659721</v>
+        <v>659678</v>
       </c>
       <c r="R78" t="n">
-        <v>7189669</v>
+        <v>7189811</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412244</v>
+        <v>127412276</v>
       </c>
       <c r="B79" t="n">
-        <v>92632</v>
+        <v>78685</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659678</v>
+        <v>659721</v>
       </c>
       <c r="R79" t="n">
-        <v>7189811</v>
+        <v>7189669</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412240</v>
+        <v>127412281</v>
       </c>
       <c r="B87" t="n">
-        <v>92624</v>
+        <v>78777</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659675</v>
+        <v>659533</v>
       </c>
       <c r="R87" t="n">
-        <v>7189819</v>
+        <v>7189693</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B88" t="n">
-        <v>92648</v>
+        <v>92624</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R88" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412307</v>
+        <v>127412248</v>
       </c>
       <c r="B89" t="n">
-        <v>92612</v>
+        <v>92648</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +10012,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659574</v>
+        <v>659638</v>
       </c>
       <c r="R89" t="n">
-        <v>7189797</v>
+        <v>7189786</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,7 +10107,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412310</v>
+        <v>127412307</v>
       </c>
       <c r="B90" t="n">
         <v>92612</v>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659559</v>
+        <v>659574</v>
       </c>
       <c r="R90" t="n">
-        <v>7189813</v>
+        <v>7189797</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412287</v>
+        <v>127412310</v>
       </c>
       <c r="B91" t="n">
-        <v>78776</v>
+        <v>92612</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659455</v>
+        <v>659559</v>
       </c>
       <c r="R91" t="n">
-        <v>7189725</v>
+        <v>7189813</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412283</v>
+        <v>127412287</v>
       </c>
       <c r="B92" t="n">
         <v>78776</v>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659523</v>
+        <v>659455</v>
       </c>
       <c r="R92" t="n">
-        <v>7189683</v>
+        <v>7189725</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B93" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R93" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92612</v>
+        <v>92636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,7 +10637,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
         <v>92636</v>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B96" t="n">
-        <v>92636</v>
+        <v>92612</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R96" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>90133</v>
+        <v>90135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127412274</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>127412277</v>
       </c>
       <c r="B23" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>127412282</v>
       </c>
       <c r="B24" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>127412319</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>127412292</v>
       </c>
       <c r="B26" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412258</v>
       </c>
       <c r="B28" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412305</v>
       </c>
       <c r="B29" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412309</v>
       </c>
       <c r="B30" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412256</v>
       </c>
       <c r="B31" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412247</v>
+        <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>90133</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659638</v>
+        <v>659629</v>
       </c>
       <c r="R32" t="n">
-        <v>7189791</v>
+        <v>7189751</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4068,7 +4068,7 @@
         <v>127412295</v>
       </c>
       <c r="B33" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412255</v>
+        <v>127412247</v>
       </c>
       <c r="B34" t="n">
-        <v>92632</v>
+        <v>90135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659629</v>
+        <v>659638</v>
       </c>
       <c r="R34" t="n">
-        <v>7189751</v>
+        <v>7189791</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412297</v>
+        <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>92632</v>
+        <v>92610</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659438</v>
+        <v>659582</v>
       </c>
       <c r="R38" t="n">
-        <v>7189796</v>
+        <v>7189797</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>92608</v>
+        <v>92634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4810,7 +4810,7 @@
         <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>127412315</v>
       </c>
       <c r="B41" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>127412271</v>
       </c>
       <c r="B42" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412261</v>
+        <v>127412301</v>
       </c>
       <c r="B43" t="n">
-        <v>92636</v>
+        <v>92614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659600</v>
+        <v>659617</v>
       </c>
       <c r="R43" t="n">
-        <v>7189733</v>
+        <v>7189798</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412278</v>
+        <v>127412261</v>
       </c>
       <c r="B44" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659622</v>
+        <v>659600</v>
       </c>
       <c r="R44" t="n">
-        <v>7189650</v>
+        <v>7189733</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412239</v>
+        <v>127412251</v>
       </c>
       <c r="B45" t="n">
-        <v>78685</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659675</v>
+        <v>659673</v>
       </c>
       <c r="R45" t="n">
-        <v>7189819</v>
+        <v>7189773</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412251</v>
+        <v>127412278</v>
       </c>
       <c r="B46" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659673</v>
+        <v>659622</v>
       </c>
       <c r="R46" t="n">
-        <v>7189773</v>
+        <v>7189650</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412301</v>
+        <v>127412259</v>
       </c>
       <c r="B47" t="n">
-        <v>92612</v>
+        <v>90135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R47" t="n">
-        <v>7189798</v>
+        <v>7189736</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412259</v>
+        <v>127412239</v>
       </c>
       <c r="B48" t="n">
-        <v>90133</v>
+        <v>78687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659620</v>
+        <v>659675</v>
       </c>
       <c r="R48" t="n">
-        <v>7189736</v>
+        <v>7189819</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412269</v>
+        <v>127412273</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,21 +5878,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>659696</v>
+        <v>659657</v>
       </c>
       <c r="R50" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412273</v>
+        <v>127412269</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>78778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,21 +5984,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>659657</v>
+        <v>659696</v>
       </c>
       <c r="R51" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B52" t="n">
-        <v>90133</v>
+        <v>90135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R52" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B53" t="n">
-        <v>90133</v>
+        <v>90135</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R53" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412304</v>
+        <v>127412293</v>
       </c>
       <c r="B54" t="n">
-        <v>92612</v>
+        <v>78779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659596</v>
+        <v>659520</v>
       </c>
       <c r="R54" t="n">
-        <v>7189785</v>
+        <v>7189812</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412280</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>92612</v>
+        <v>92638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659557</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189710</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412241</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>78776</v>
+        <v>92614</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412268</v>
+        <v>127412279</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>92638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659696</v>
+        <v>659576</v>
       </c>
       <c r="R57" t="n">
-        <v>7189717</v>
+        <v>7189699</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412243</v>
+        <v>127412280</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>92614</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659557</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189710</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412318</v>
+        <v>127412241</v>
       </c>
       <c r="B59" t="n">
-        <v>92636</v>
+        <v>78778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659479</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189697</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412279</v>
+        <v>127412268</v>
       </c>
       <c r="B60" t="n">
-        <v>92636</v>
+        <v>79638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659576</v>
+        <v>659696</v>
       </c>
       <c r="R60" t="n">
-        <v>7189699</v>
+        <v>7189717</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412243</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412299</v>
+        <v>127412272</v>
       </c>
       <c r="B62" t="n">
-        <v>78776</v>
+        <v>79638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>659637</v>
+        <v>659634</v>
       </c>
       <c r="R62" t="n">
-        <v>7189827</v>
+        <v>7189692</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412272</v>
+        <v>127412299</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>78778</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,21 +7256,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>659634</v>
+        <v>659637</v>
       </c>
       <c r="R63" t="n">
-        <v>7189692</v>
+        <v>7189827</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412286</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>92616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189705</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412267</v>
+        <v>127412312</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>92616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659676</v>
+        <v>659563</v>
       </c>
       <c r="R65" t="n">
-        <v>7189721</v>
+        <v>7189659</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412270</v>
+        <v>127412316</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>92638</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659696</v>
+        <v>659527</v>
       </c>
       <c r="R66" t="n">
-        <v>7189717</v>
+        <v>7189674</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412316</v>
+        <v>127412265</v>
       </c>
       <c r="B67" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659527</v>
+        <v>659682</v>
       </c>
       <c r="R67" t="n">
-        <v>7189674</v>
+        <v>7189733</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412265</v>
+        <v>127412317</v>
       </c>
       <c r="B68" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659682</v>
+        <v>659491</v>
       </c>
       <c r="R68" t="n">
-        <v>7189733</v>
+        <v>7189693</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412317</v>
+        <v>127412270</v>
       </c>
       <c r="B69" t="n">
-        <v>92636</v>
+        <v>78779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R69" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412245</v>
+        <v>127412286</v>
       </c>
       <c r="B70" t="n">
-        <v>92614</v>
+        <v>79609</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R70" t="n">
-        <v>7189799</v>
+        <v>7189705</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412312</v>
+        <v>127412267</v>
       </c>
       <c r="B71" t="n">
-        <v>92614</v>
+        <v>79609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659563</v>
+        <v>659676</v>
       </c>
       <c r="R71" t="n">
-        <v>7189659</v>
+        <v>7189721</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8202,7 +8202,7 @@
         <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412252</v>
+        <v>127412262</v>
       </c>
       <c r="B73" t="n">
-        <v>90133</v>
+        <v>92638</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659674</v>
+        <v>659670</v>
       </c>
       <c r="R73" t="n">
-        <v>7189772</v>
+        <v>7189732</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412285</v>
+        <v>127412242</v>
       </c>
       <c r="B74" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R74" t="n">
-        <v>7189705</v>
+        <v>7189813</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412262</v>
+        <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>92636</v>
+        <v>78778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659670</v>
+        <v>659491</v>
       </c>
       <c r="R75" t="n">
-        <v>7189732</v>
+        <v>7189705</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412242</v>
+        <v>127412252</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>90135</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659677</v>
+        <v>659674</v>
       </c>
       <c r="R76" t="n">
-        <v>7189813</v>
+        <v>7189772</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8732,7 +8732,7 @@
         <v>127412254</v>
       </c>
       <c r="B77" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>127412244</v>
       </c>
       <c r="B78" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>127412276</v>
       </c>
       <c r="B79" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412266</v>
       </c>
       <c r="B83" t="n">
-        <v>78685</v>
+        <v>92616</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659689</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189728</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>92616</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R84" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412296</v>
+        <v>127412284</v>
       </c>
       <c r="B85" t="n">
-        <v>92614</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659476</v>
+        <v>659491</v>
       </c>
       <c r="R85" t="n">
-        <v>7189791</v>
+        <v>7189705</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412266</v>
+        <v>127412308</v>
       </c>
       <c r="B86" t="n">
-        <v>92614</v>
+        <v>78687</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659689</v>
+        <v>659555</v>
       </c>
       <c r="R86" t="n">
-        <v>7189728</v>
+        <v>7189806</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412281</v>
+        <v>127412310</v>
       </c>
       <c r="B87" t="n">
-        <v>78777</v>
+        <v>92614</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659533</v>
+        <v>659559</v>
       </c>
       <c r="R87" t="n">
-        <v>7189693</v>
+        <v>7189813</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412240</v>
+        <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>92624</v>
+        <v>92614</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659675</v>
+        <v>659574</v>
       </c>
       <c r="R88" t="n">
-        <v>7189819</v>
+        <v>7189797</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B89" t="n">
-        <v>92648</v>
+        <v>92626</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R89" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412307</v>
+        <v>127412287</v>
       </c>
       <c r="B90" t="n">
-        <v>92612</v>
+        <v>78778</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659574</v>
+        <v>659455</v>
       </c>
       <c r="R90" t="n">
-        <v>7189797</v>
+        <v>7189725</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412310</v>
+        <v>127412248</v>
       </c>
       <c r="B91" t="n">
-        <v>92612</v>
+        <v>92650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659559</v>
+        <v>659638</v>
       </c>
       <c r="R91" t="n">
-        <v>7189813</v>
+        <v>7189786</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412287</v>
+        <v>127412283</v>
       </c>
       <c r="B92" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659455</v>
+        <v>659523</v>
       </c>
       <c r="R92" t="n">
-        <v>7189725</v>
+        <v>7189683</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412283</v>
+        <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659523</v>
+        <v>659533</v>
       </c>
       <c r="R93" t="n">
-        <v>7189683</v>
+        <v>7189693</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10534,7 +10534,7 @@
         <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92636</v>
+        <v>92638</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B95" t="n">
-        <v>92636</v>
+        <v>92614</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B96" t="n">
-        <v>92612</v>
+        <v>92638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R96" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B20" t="n">
-        <v>92638</v>
+        <v>90135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R20" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90135</v>
+        <v>92638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>92616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R25" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>92634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R26" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412295</v>
+        <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>78778</v>
+        <v>90135</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659512</v>
+        <v>659638</v>
       </c>
       <c r="R33" t="n">
-        <v>7189786</v>
+        <v>7189791</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412247</v>
+        <v>127412295</v>
       </c>
       <c r="B34" t="n">
-        <v>90135</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659638</v>
+        <v>659512</v>
       </c>
       <c r="R34" t="n">
-        <v>7189791</v>
+        <v>7189786</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412301</v>
+        <v>127412261</v>
       </c>
       <c r="B43" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659617</v>
+        <v>659600</v>
       </c>
       <c r="R43" t="n">
-        <v>7189798</v>
+        <v>7189733</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412261</v>
+        <v>127412278</v>
       </c>
       <c r="B44" t="n">
         <v>92638</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659600</v>
+        <v>659622</v>
       </c>
       <c r="R44" t="n">
-        <v>7189733</v>
+        <v>7189650</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412278</v>
+        <v>127412301</v>
       </c>
       <c r="B46" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659622</v>
+        <v>659617</v>
       </c>
       <c r="R46" t="n">
-        <v>7189650</v>
+        <v>7189798</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B52" t="n">
         <v>90135</v>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R52" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B53" t="n">
         <v>90135</v>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R53" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412293</v>
+        <v>127412304</v>
       </c>
       <c r="B54" t="n">
-        <v>78779</v>
+        <v>92614</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659520</v>
+        <v>659596</v>
       </c>
       <c r="R54" t="n">
-        <v>7189812</v>
+        <v>7189785</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412280</v>
       </c>
       <c r="B55" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659557</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189710</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412241</v>
       </c>
       <c r="B56" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659677</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189813</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412279</v>
+        <v>127412268</v>
       </c>
       <c r="B57" t="n">
-        <v>92638</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659576</v>
+        <v>659696</v>
       </c>
       <c r="R57" t="n">
-        <v>7189699</v>
+        <v>7189717</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412280</v>
+        <v>127412243</v>
       </c>
       <c r="B58" t="n">
-        <v>92614</v>
+        <v>79638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659557</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189710</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412241</v>
+        <v>127412318</v>
       </c>
       <c r="B59" t="n">
-        <v>78778</v>
+        <v>92638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412268</v>
+        <v>127412279</v>
       </c>
       <c r="B60" t="n">
-        <v>79638</v>
+        <v>92638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659696</v>
+        <v>659576</v>
       </c>
       <c r="R60" t="n">
-        <v>7189717</v>
+        <v>7189699</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412243</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412272</v>
+        <v>127412299</v>
       </c>
       <c r="B62" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>659634</v>
+        <v>659637</v>
       </c>
       <c r="R62" t="n">
-        <v>7189692</v>
+        <v>7189827</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412299</v>
+        <v>127412272</v>
       </c>
       <c r="B63" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,21 +7256,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>659637</v>
+        <v>659634</v>
       </c>
       <c r="R63" t="n">
-        <v>7189827</v>
+        <v>7189692</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412286</v>
       </c>
       <c r="B64" t="n">
-        <v>92616</v>
+        <v>79609</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189705</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412312</v>
+        <v>127412267</v>
       </c>
       <c r="B65" t="n">
-        <v>92616</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659563</v>
+        <v>659676</v>
       </c>
       <c r="R65" t="n">
-        <v>7189659</v>
+        <v>7189721</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412316</v>
+        <v>127412270</v>
       </c>
       <c r="B66" t="n">
-        <v>92638</v>
+        <v>78779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659527</v>
+        <v>659696</v>
       </c>
       <c r="R66" t="n">
-        <v>7189674</v>
+        <v>7189717</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B67" t="n">
         <v>92638</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R67" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412317</v>
+        <v>127412265</v>
       </c>
       <c r="B68" t="n">
         <v>92638</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659491</v>
+        <v>659682</v>
       </c>
       <c r="R68" t="n">
-        <v>7189693</v>
+        <v>7189733</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412270</v>
+        <v>127412317</v>
       </c>
       <c r="B69" t="n">
-        <v>78779</v>
+        <v>92638</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412286</v>
+        <v>127412245</v>
       </c>
       <c r="B70" t="n">
-        <v>79609</v>
+        <v>92616</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R70" t="n">
-        <v>7189705</v>
+        <v>7189799</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412267</v>
+        <v>127412312</v>
       </c>
       <c r="B71" t="n">
-        <v>79609</v>
+        <v>92616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659676</v>
+        <v>659563</v>
       </c>
       <c r="R71" t="n">
-        <v>7189721</v>
+        <v>7189659</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412253</v>
+        <v>127412252</v>
       </c>
       <c r="B72" t="n">
-        <v>92622</v>
+        <v>90135</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659620</v>
+        <v>659674</v>
       </c>
       <c r="R72" t="n">
-        <v>7189750</v>
+        <v>7189772</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412262</v>
+        <v>127412285</v>
       </c>
       <c r="B73" t="n">
-        <v>92638</v>
+        <v>78778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659670</v>
+        <v>659491</v>
       </c>
       <c r="R73" t="n">
-        <v>7189732</v>
+        <v>7189705</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412242</v>
+        <v>127412262</v>
       </c>
       <c r="B74" t="n">
-        <v>78779</v>
+        <v>92638</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659677</v>
+        <v>659670</v>
       </c>
       <c r="R74" t="n">
-        <v>7189813</v>
+        <v>7189732</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412253</v>
       </c>
       <c r="B75" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659620</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189750</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>90135</v>
+        <v>78779</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R76" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,32 +8729,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412254</v>
+        <v>127412244</v>
       </c>
       <c r="B77" t="n">
-        <v>92638</v>
+        <v>92634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659613</v>
+        <v>659678</v>
       </c>
       <c r="R77" t="n">
-        <v>7189750</v>
+        <v>7189811</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,32 +8835,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412244</v>
+        <v>127412276</v>
       </c>
       <c r="B78" t="n">
-        <v>92634</v>
+        <v>78687</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659678</v>
+        <v>659721</v>
       </c>
       <c r="R78" t="n">
-        <v>7189811</v>
+        <v>7189669</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412276</v>
+        <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>78687</v>
+        <v>92638</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659721</v>
+        <v>659613</v>
       </c>
       <c r="R79" t="n">
-        <v>7189669</v>
+        <v>7189750</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412266</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92616</v>
+        <v>78687</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659689</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189728</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412284</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>92616</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659491</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189705</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412308</v>
+        <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659555</v>
+        <v>659491</v>
       </c>
       <c r="R86" t="n">
-        <v>7189806</v>
+        <v>7189705</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412310</v>
+        <v>127412281</v>
       </c>
       <c r="B87" t="n">
-        <v>92614</v>
+        <v>78779</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659559</v>
+        <v>659533</v>
       </c>
       <c r="R87" t="n">
-        <v>7189813</v>
+        <v>7189693</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412307</v>
+        <v>127412248</v>
       </c>
       <c r="B88" t="n">
-        <v>92614</v>
+        <v>92650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659574</v>
+        <v>659638</v>
       </c>
       <c r="R88" t="n">
-        <v>7189797</v>
+        <v>7189786</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412287</v>
+        <v>127412307</v>
       </c>
       <c r="B90" t="n">
-        <v>78778</v>
+        <v>92614</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659455</v>
+        <v>659574</v>
       </c>
       <c r="R90" t="n">
-        <v>7189725</v>
+        <v>7189797</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412248</v>
+        <v>127412310</v>
       </c>
       <c r="B91" t="n">
-        <v>92650</v>
+        <v>92614</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659638</v>
+        <v>659559</v>
       </c>
       <c r="R91" t="n">
-        <v>7189786</v>
+        <v>7189813</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412283</v>
+        <v>127412287</v>
       </c>
       <c r="B92" t="n">
         <v>78778</v>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659523</v>
+        <v>659455</v>
       </c>
       <c r="R92" t="n">
-        <v>7189683</v>
+        <v>7189725</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B93" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R93" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B96" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R96" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>90135</v>
+        <v>92638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>92638</v>
+        <v>90135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412306</v>
+        <v>127412294</v>
       </c>
       <c r="B38" t="n">
-        <v>92610</v>
+        <v>78778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659582</v>
+        <v>659520</v>
       </c>
       <c r="R38" t="n">
-        <v>7189797</v>
+        <v>7189812</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412306</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>92610</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659582</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189797</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B40" t="n">
-        <v>78778</v>
+        <v>92634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R40" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412315</v>
+        <v>127412239</v>
       </c>
       <c r="B41" t="n">
-        <v>90367</v>
+        <v>78687</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659538</v>
+        <v>659675</v>
       </c>
       <c r="R41" t="n">
-        <v>7189669</v>
+        <v>7189819</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412271</v>
+        <v>127412315</v>
       </c>
       <c r="B42" t="n">
-        <v>92638</v>
+        <v>90367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659620</v>
+        <v>659538</v>
       </c>
       <c r="R42" t="n">
-        <v>7189703</v>
+        <v>7189669</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412261</v>
+        <v>127412271</v>
       </c>
       <c r="B43" t="n">
         <v>92638</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659600</v>
+        <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189733</v>
+        <v>7189703</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412278</v>
+        <v>127412261</v>
       </c>
       <c r="B44" t="n">
         <v>92638</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659622</v>
+        <v>659600</v>
       </c>
       <c r="R44" t="n">
-        <v>7189650</v>
+        <v>7189733</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412251</v>
+        <v>127412278</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>92638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659673</v>
+        <v>659622</v>
       </c>
       <c r="R45" t="n">
-        <v>7189773</v>
+        <v>7189650</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412301</v>
+        <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659617</v>
+        <v>659673</v>
       </c>
       <c r="R46" t="n">
-        <v>7189798</v>
+        <v>7189773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412259</v>
+        <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>90135</v>
+        <v>92614</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R47" t="n">
-        <v>7189736</v>
+        <v>7189798</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412239</v>
+        <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>78687</v>
+        <v>90135</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659675</v>
+        <v>659620</v>
       </c>
       <c r="R48" t="n">
-        <v>7189819</v>
+        <v>7189736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412304</v>
+        <v>127412293</v>
       </c>
       <c r="B54" t="n">
-        <v>92614</v>
+        <v>78779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659596</v>
+        <v>659520</v>
       </c>
       <c r="R54" t="n">
-        <v>7189785</v>
+        <v>7189812</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412280</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659557</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189710</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412241</v>
+        <v>127412279</v>
       </c>
       <c r="B56" t="n">
-        <v>78778</v>
+        <v>92638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659576</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189699</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B59" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R59" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B60" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R60" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412241</v>
       </c>
       <c r="B61" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412276</v>
+        <v>127412275</v>
       </c>
       <c r="B78" t="n">
-        <v>78687</v>
+        <v>79638</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659721</v>
+        <v>659650</v>
       </c>
       <c r="R78" t="n">
-        <v>7189669</v>
+        <v>7189690</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B79" t="n">
-        <v>92638</v>
+        <v>78687</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R79" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412275</v>
+        <v>127412254</v>
       </c>
       <c r="B80" t="n">
-        <v>79638</v>
+        <v>92638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659650</v>
+        <v>659613</v>
       </c>
       <c r="R80" t="n">
-        <v>7189690</v>
+        <v>7189750</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B81" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R81" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B82" t="n">
-        <v>78778</v>
+        <v>92614</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R82" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412281</v>
+        <v>127412248</v>
       </c>
       <c r="B87" t="n">
-        <v>78779</v>
+        <v>92650</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659533</v>
+        <v>659638</v>
       </c>
       <c r="R87" t="n">
-        <v>7189693</v>
+        <v>7189786</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B88" t="n">
-        <v>92650</v>
+        <v>92626</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R88" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412240</v>
+        <v>127412307</v>
       </c>
       <c r="B89" t="n">
-        <v>92626</v>
+        <v>92614</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659675</v>
+        <v>659574</v>
       </c>
       <c r="R89" t="n">
-        <v>7189819</v>
+        <v>7189797</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,7 +10107,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412307</v>
+        <v>127412310</v>
       </c>
       <c r="B90" t="n">
         <v>92614</v>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659574</v>
+        <v>659559</v>
       </c>
       <c r="R90" t="n">
-        <v>7189797</v>
+        <v>7189813</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412310</v>
+        <v>127412287</v>
       </c>
       <c r="B91" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659559</v>
+        <v>659455</v>
       </c>
       <c r="R91" t="n">
-        <v>7189813</v>
+        <v>7189725</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412287</v>
+        <v>127412283</v>
       </c>
       <c r="B92" t="n">
         <v>78778</v>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659455</v>
+        <v>659523</v>
       </c>
       <c r="R92" t="n">
-        <v>7189725</v>
+        <v>7189683</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412283</v>
+        <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659523</v>
+        <v>659533</v>
       </c>
       <c r="R93" t="n">
-        <v>7189683</v>
+        <v>7189693</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B20" t="n">
-        <v>92638</v>
+        <v>90135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R20" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90135</v>
+        <v>92638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412277</v>
+        <v>127412292</v>
       </c>
       <c r="B23" t="n">
-        <v>92638</v>
+        <v>92616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659674</v>
+        <v>659492</v>
       </c>
       <c r="R23" t="n">
-        <v>7189662</v>
+        <v>7189757</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412282</v>
+        <v>127412277</v>
       </c>
       <c r="B24" t="n">
         <v>92638</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659532</v>
+        <v>659674</v>
       </c>
       <c r="R24" t="n">
-        <v>7189692</v>
+        <v>7189662</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B25" t="n">
-        <v>92616</v>
+        <v>92634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R25" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412319</v>
+        <v>127412282</v>
       </c>
       <c r="B26" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659459</v>
+        <v>659532</v>
       </c>
       <c r="R26" t="n">
-        <v>7189700</v>
+        <v>7189692</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412258</v>
+        <v>127412256</v>
       </c>
       <c r="B28" t="n">
         <v>92638</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659663</v>
+        <v>659665</v>
       </c>
       <c r="R28" t="n">
-        <v>7189743</v>
+        <v>7189754</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>92638</v>
+        <v>90367</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R29" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412309</v>
+        <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>90367</v>
+        <v>92638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659555</v>
+        <v>659567</v>
       </c>
       <c r="R30" t="n">
-        <v>7189806</v>
+        <v>7189783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412256</v>
+        <v>127412258</v>
       </c>
       <c r="B31" t="n">
         <v>92638</v>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659665</v>
+        <v>659663</v>
       </c>
       <c r="R31" t="n">
-        <v>7189754</v>
+        <v>7189743</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412255</v>
+        <v>127412247</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>90135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659629</v>
+        <v>659638</v>
       </c>
       <c r="R32" t="n">
-        <v>7189751</v>
+        <v>7189791</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412247</v>
+        <v>127412255</v>
       </c>
       <c r="B33" t="n">
-        <v>90135</v>
+        <v>92634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659638</v>
+        <v>659629</v>
       </c>
       <c r="R33" t="n">
-        <v>7189791</v>
+        <v>7189751</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>78778</v>
+        <v>92610</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R38" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>92610</v>
+        <v>92634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>92634</v>
+        <v>78778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R40" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412239</v>
+        <v>127412251</v>
       </c>
       <c r="B41" t="n">
-        <v>78687</v>
+        <v>92616</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659675</v>
+        <v>659673</v>
       </c>
       <c r="R41" t="n">
-        <v>7189819</v>
+        <v>7189773</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412315</v>
+        <v>127412301</v>
       </c>
       <c r="B42" t="n">
-        <v>90367</v>
+        <v>92614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659538</v>
+        <v>659617</v>
       </c>
       <c r="R42" t="n">
-        <v>7189669</v>
+        <v>7189798</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,32 +5125,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412271</v>
+        <v>127412259</v>
       </c>
       <c r="B43" t="n">
-        <v>92638</v>
+        <v>90135</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5167,7 +5167,7 @@
         <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189703</v>
+        <v>7189736</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412278</v>
+        <v>127412271</v>
       </c>
       <c r="B45" t="n">
         <v>92638</v>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659622</v>
+        <v>659620</v>
       </c>
       <c r="R45" t="n">
-        <v>7189650</v>
+        <v>7189703</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412251</v>
+        <v>127412278</v>
       </c>
       <c r="B46" t="n">
-        <v>92616</v>
+        <v>92638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659673</v>
+        <v>659622</v>
       </c>
       <c r="R46" t="n">
-        <v>7189773</v>
+        <v>7189650</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412301</v>
+        <v>127412315</v>
       </c>
       <c r="B47" t="n">
-        <v>92614</v>
+        <v>90367</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659617</v>
+        <v>659538</v>
       </c>
       <c r="R47" t="n">
-        <v>7189798</v>
+        <v>7189669</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412259</v>
+        <v>127412239</v>
       </c>
       <c r="B48" t="n">
-        <v>90135</v>
+        <v>78687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659620</v>
+        <v>659675</v>
       </c>
       <c r="R48" t="n">
-        <v>7189736</v>
+        <v>7189819</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412280</v>
       </c>
       <c r="B55" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659557</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189710</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412268</v>
+        <v>127412318</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>92638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659696</v>
+        <v>659479</v>
       </c>
       <c r="R57" t="n">
-        <v>7189717</v>
+        <v>7189697</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412243</v>
+        <v>127412304</v>
       </c>
       <c r="B58" t="n">
-        <v>79638</v>
+        <v>92614</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412304</v>
+        <v>127412241</v>
       </c>
       <c r="B59" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659596</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189785</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412280</v>
+        <v>127412268</v>
       </c>
       <c r="B60" t="n">
-        <v>92614</v>
+        <v>79638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659557</v>
+        <v>659696</v>
       </c>
       <c r="R60" t="n">
-        <v>7189710</v>
+        <v>7189717</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412241</v>
+        <v>127412243</v>
       </c>
       <c r="B61" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412299</v>
+        <v>127412272</v>
       </c>
       <c r="B62" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>659637</v>
+        <v>659634</v>
       </c>
       <c r="R62" t="n">
-        <v>7189827</v>
+        <v>7189692</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412272</v>
+        <v>127412299</v>
       </c>
       <c r="B63" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,21 +7256,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>659634</v>
+        <v>659637</v>
       </c>
       <c r="R63" t="n">
-        <v>7189692</v>
+        <v>7189827</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412286</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>79609</v>
+        <v>92616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189705</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412267</v>
+        <v>127412312</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>92616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659676</v>
+        <v>659563</v>
       </c>
       <c r="R65" t="n">
-        <v>7189721</v>
+        <v>7189659</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412270</v>
+        <v>127412317</v>
       </c>
       <c r="B66" t="n">
-        <v>78779</v>
+        <v>92638</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R66" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412317</v>
+        <v>127412286</v>
       </c>
       <c r="B69" t="n">
-        <v>92638</v>
+        <v>79609</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7923,7 +7923,7 @@
         <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189693</v>
+        <v>7189705</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412245</v>
+        <v>127412267</v>
       </c>
       <c r="B70" t="n">
-        <v>92616</v>
+        <v>79609</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659677</v>
+        <v>659676</v>
       </c>
       <c r="R70" t="n">
-        <v>7189799</v>
+        <v>7189721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412312</v>
+        <v>127412270</v>
       </c>
       <c r="B71" t="n">
-        <v>92616</v>
+        <v>78779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659563</v>
+        <v>659696</v>
       </c>
       <c r="R71" t="n">
-        <v>7189659</v>
+        <v>7189717</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412252</v>
+        <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>90135</v>
+        <v>92638</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659674</v>
+        <v>659670</v>
       </c>
       <c r="R72" t="n">
-        <v>7189772</v>
+        <v>7189732</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412262</v>
+        <v>127412252</v>
       </c>
       <c r="B74" t="n">
-        <v>92638</v>
+        <v>90135</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659670</v>
+        <v>659674</v>
       </c>
       <c r="R74" t="n">
-        <v>7189732</v>
+        <v>7189772</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412275</v>
+        <v>127412276</v>
       </c>
       <c r="B78" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659650</v>
+        <v>659721</v>
       </c>
       <c r="R78" t="n">
-        <v>7189690</v>
+        <v>7189669</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412276</v>
+        <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>78687</v>
+        <v>92638</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659721</v>
+        <v>659613</v>
       </c>
       <c r="R79" t="n">
-        <v>7189669</v>
+        <v>7189750</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412254</v>
+        <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>92638</v>
+        <v>79638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9058,21 +9058,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659613</v>
+        <v>659650</v>
       </c>
       <c r="R80" t="n">
-        <v>7189750</v>
+        <v>7189690</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>78778</v>
+        <v>92614</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R81" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R82" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412266</v>
       </c>
       <c r="B83" t="n">
-        <v>78687</v>
+        <v>92616</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659689</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189728</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412296</v>
+        <v>127412284</v>
       </c>
       <c r="B84" t="n">
-        <v>92616</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659476</v>
+        <v>659491</v>
       </c>
       <c r="R84" t="n">
-        <v>7189791</v>
+        <v>7189705</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B85" t="n">
         <v>92616</v>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412284</v>
+        <v>127412308</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659491</v>
+        <v>659555</v>
       </c>
       <c r="R86" t="n">
-        <v>7189705</v>
+        <v>7189806</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412240</v>
+        <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>92626</v>
+        <v>92614</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659675</v>
+        <v>659574</v>
       </c>
       <c r="R88" t="n">
-        <v>7189819</v>
+        <v>7189797</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,7 +10001,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412307</v>
+        <v>127412310</v>
       </c>
       <c r="B89" t="n">
         <v>92614</v>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659574</v>
+        <v>659559</v>
       </c>
       <c r="R89" t="n">
-        <v>7189797</v>
+        <v>7189813</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,32 +10107,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412310</v>
+        <v>127412240</v>
       </c>
       <c r="B90" t="n">
-        <v>92614</v>
+        <v>92626</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659559</v>
+        <v>659675</v>
       </c>
       <c r="R90" t="n">
-        <v>7189813</v>
+        <v>7189819</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B94" t="n">
-        <v>92638</v>
+        <v>92614</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R94" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B96" t="n">
-        <v>92614</v>
+        <v>92638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R96" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,32 +2687,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>90135</v>
+        <v>92644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>92638</v>
+        <v>90141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412292</v>
+        <v>127412282</v>
       </c>
       <c r="B23" t="n">
-        <v>92616</v>
+        <v>92644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659492</v>
+        <v>659532</v>
       </c>
       <c r="R23" t="n">
-        <v>7189757</v>
+        <v>7189692</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3114,7 +3114,7 @@
         <v>127412277</v>
       </c>
       <c r="B24" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>92622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R25" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412282</v>
+        <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659532</v>
+        <v>659459</v>
       </c>
       <c r="R26" t="n">
-        <v>7189692</v>
+        <v>7189700</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412256</v>
       </c>
       <c r="B28" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>90367</v>
+        <v>90373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412258</v>
       </c>
       <c r="B31" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412247</v>
+        <v>127412295</v>
       </c>
       <c r="B32" t="n">
-        <v>90135</v>
+        <v>78778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659638</v>
+        <v>659512</v>
       </c>
       <c r="R32" t="n">
-        <v>7189791</v>
+        <v>7189786</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412255</v>
+        <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>92634</v>
+        <v>90141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659629</v>
+        <v>659638</v>
       </c>
       <c r="R33" t="n">
-        <v>7189751</v>
+        <v>7189791</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412295</v>
+        <v>127412255</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>92640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659512</v>
+        <v>659629</v>
       </c>
       <c r="R34" t="n">
-        <v>7189786</v>
+        <v>7189751</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B38" t="n">
-        <v>92610</v>
+        <v>92640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R38" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>78778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B40" t="n">
-        <v>78778</v>
+        <v>92616</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R40" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412251</v>
+        <v>127412239</v>
       </c>
       <c r="B41" t="n">
-        <v>92616</v>
+        <v>78687</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659673</v>
+        <v>659675</v>
       </c>
       <c r="R41" t="n">
-        <v>7189773</v>
+        <v>7189819</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412301</v>
+        <v>127412251</v>
       </c>
       <c r="B42" t="n">
-        <v>92614</v>
+        <v>92622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659617</v>
+        <v>659673</v>
       </c>
       <c r="R42" t="n">
-        <v>7189798</v>
+        <v>7189773</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,32 +5125,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412259</v>
+        <v>127412301</v>
       </c>
       <c r="B43" t="n">
-        <v>90135</v>
+        <v>92620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R43" t="n">
-        <v>7189736</v>
+        <v>7189798</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,32 +5231,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412261</v>
+        <v>127412259</v>
       </c>
       <c r="B44" t="n">
-        <v>92638</v>
+        <v>90141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659600</v>
+        <v>659620</v>
       </c>
       <c r="R44" t="n">
-        <v>7189733</v>
+        <v>7189736</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412271</v>
+        <v>127412261</v>
       </c>
       <c r="B45" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659620</v>
+        <v>659600</v>
       </c>
       <c r="R45" t="n">
-        <v>7189703</v>
+        <v>7189733</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412278</v>
+        <v>127412271</v>
       </c>
       <c r="B46" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659622</v>
+        <v>659620</v>
       </c>
       <c r="R46" t="n">
-        <v>7189650</v>
+        <v>7189703</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412315</v>
+        <v>127412278</v>
       </c>
       <c r="B47" t="n">
-        <v>90367</v>
+        <v>92644</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659538</v>
+        <v>659622</v>
       </c>
       <c r="R47" t="n">
-        <v>7189669</v>
+        <v>7189650</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412239</v>
+        <v>127412315</v>
       </c>
       <c r="B48" t="n">
-        <v>78687</v>
+        <v>90373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,21 +5666,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659675</v>
+        <v>659538</v>
       </c>
       <c r="R48" t="n">
-        <v>7189819</v>
+        <v>7189669</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>127412291</v>
       </c>
       <c r="B52" t="n">
-        <v>90135</v>
+        <v>90141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127412250</v>
       </c>
       <c r="B53" t="n">
-        <v>90135</v>
+        <v>90141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412293</v>
+        <v>127412304</v>
       </c>
       <c r="B54" t="n">
-        <v>78779</v>
+        <v>92620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659520</v>
+        <v>659596</v>
       </c>
       <c r="R54" t="n">
-        <v>7189812</v>
+        <v>7189785</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6400,7 +6400,7 @@
         <v>127412280</v>
       </c>
       <c r="B55" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>127412279</v>
       </c>
       <c r="B56" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>127412318</v>
       </c>
       <c r="B57" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412304</v>
+        <v>127412241</v>
       </c>
       <c r="B58" t="n">
-        <v>92614</v>
+        <v>78778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659596</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189785</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412241</v>
+        <v>127412268</v>
       </c>
       <c r="B59" t="n">
-        <v>78778</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659696</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189717</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412268</v>
+        <v>127412243</v>
       </c>
       <c r="B60" t="n">
         <v>79638</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R60" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412243</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412286</v>
       </c>
       <c r="B64" t="n">
-        <v>92616</v>
+        <v>79609</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189705</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412312</v>
+        <v>127412267</v>
       </c>
       <c r="B65" t="n">
-        <v>92616</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659563</v>
+        <v>659676</v>
       </c>
       <c r="R65" t="n">
-        <v>7189659</v>
+        <v>7189721</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412317</v>
+        <v>127412270</v>
       </c>
       <c r="B66" t="n">
-        <v>92638</v>
+        <v>78779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R66" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412316</v>
+        <v>127412317</v>
       </c>
       <c r="B67" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659527</v>
+        <v>659491</v>
       </c>
       <c r="R67" t="n">
-        <v>7189674</v>
+        <v>7189693</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B68" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R68" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412286</v>
+        <v>127412265</v>
       </c>
       <c r="B69" t="n">
-        <v>79609</v>
+        <v>92644</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659491</v>
+        <v>659682</v>
       </c>
       <c r="R69" t="n">
-        <v>7189705</v>
+        <v>7189733</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412267</v>
+        <v>127412245</v>
       </c>
       <c r="B70" t="n">
-        <v>79609</v>
+        <v>92622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659676</v>
+        <v>659677</v>
       </c>
       <c r="R70" t="n">
-        <v>7189721</v>
+        <v>7189799</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412270</v>
+        <v>127412312</v>
       </c>
       <c r="B71" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659696</v>
+        <v>659563</v>
       </c>
       <c r="R71" t="n">
-        <v>7189717</v>
+        <v>7189659</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8202,7 +8202,7 @@
         <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412285</v>
+        <v>127412252</v>
       </c>
       <c r="B73" t="n">
-        <v>78778</v>
+        <v>90141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659491</v>
+        <v>659674</v>
       </c>
       <c r="R73" t="n">
-        <v>7189705</v>
+        <v>7189772</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412252</v>
+        <v>127412253</v>
       </c>
       <c r="B74" t="n">
-        <v>90135</v>
+        <v>92628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659674</v>
+        <v>659620</v>
       </c>
       <c r="R74" t="n">
-        <v>7189772</v>
+        <v>7189750</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412253</v>
+        <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659620</v>
+        <v>659491</v>
       </c>
       <c r="R75" t="n">
-        <v>7189750</v>
+        <v>7189705</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8729,32 +8729,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412244</v>
+        <v>127412254</v>
       </c>
       <c r="B77" t="n">
-        <v>92634</v>
+        <v>92644</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659678</v>
+        <v>659613</v>
       </c>
       <c r="R77" t="n">
-        <v>7189811</v>
+        <v>7189750</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412254</v>
+        <v>127412244</v>
       </c>
       <c r="B79" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659613</v>
+        <v>659678</v>
       </c>
       <c r="R79" t="n">
-        <v>7189750</v>
+        <v>7189811</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
         <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412266</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92616</v>
+        <v>78687</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659689</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189728</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R84" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412296</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659476</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189791</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412308</v>
+        <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659555</v>
+        <v>659491</v>
       </c>
       <c r="R86" t="n">
-        <v>7189806</v>
+        <v>7189705</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B87" t="n">
-        <v>92650</v>
+        <v>92632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R87" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9898,7 +9898,7 @@
         <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>127412310</v>
       </c>
       <c r="B89" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10107,32 +10107,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412240</v>
+        <v>127412248</v>
       </c>
       <c r="B90" t="n">
-        <v>92626</v>
+        <v>92656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659675</v>
+        <v>659638</v>
       </c>
       <c r="R90" t="n">
-        <v>7189819</v>
+        <v>7189786</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B94" t="n">
-        <v>92614</v>
+        <v>92644</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B95" t="n">
-        <v>92638</v>
+        <v>92644</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B96" t="n">
-        <v>92638</v>
+        <v>92620</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412274</v>
       </c>
       <c r="B21" t="n">
-        <v>90141</v>
+        <v>78782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659657</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189693</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>90144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R22" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3008,7 +3008,7 @@
         <v>127412282</v>
       </c>
       <c r="B23" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>127412277</v>
       </c>
       <c r="B24" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412256</v>
       </c>
       <c r="B28" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>90373</v>
+        <v>90376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412258</v>
       </c>
       <c r="B31" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>127412295</v>
       </c>
       <c r="B32" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>90141</v>
+        <v>90144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127412255</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B38" t="n">
-        <v>92640</v>
+        <v>78781</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R38" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>78778</v>
+        <v>92643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4810,7 +4810,7 @@
         <v>127412306</v>
       </c>
       <c r="B40" t="n">
-        <v>92616</v>
+        <v>92619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>127412239</v>
       </c>
       <c r="B41" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412251</v>
+        <v>127412261</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>92647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659673</v>
+        <v>659600</v>
       </c>
       <c r="R42" t="n">
-        <v>7189773</v>
+        <v>7189733</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412301</v>
+        <v>127412271</v>
       </c>
       <c r="B43" t="n">
-        <v>92620</v>
+        <v>92647</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189798</v>
+        <v>7189703</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,32 +5231,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412259</v>
+        <v>127412278</v>
       </c>
       <c r="B44" t="n">
-        <v>90141</v>
+        <v>92647</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659620</v>
+        <v>659622</v>
       </c>
       <c r="R44" t="n">
-        <v>7189736</v>
+        <v>7189650</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412261</v>
+        <v>127412315</v>
       </c>
       <c r="B45" t="n">
-        <v>92644</v>
+        <v>90376</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659600</v>
+        <v>659538</v>
       </c>
       <c r="R45" t="n">
-        <v>7189733</v>
+        <v>7189669</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412271</v>
+        <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92644</v>
+        <v>92625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659620</v>
+        <v>659673</v>
       </c>
       <c r="R46" t="n">
-        <v>7189703</v>
+        <v>7189773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412278</v>
+        <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>92644</v>
+        <v>92623</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659622</v>
+        <v>659617</v>
       </c>
       <c r="R47" t="n">
-        <v>7189650</v>
+        <v>7189798</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412315</v>
+        <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>90373</v>
+        <v>90144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659538</v>
+        <v>659620</v>
       </c>
       <c r="R48" t="n">
-        <v>7189669</v>
+        <v>7189736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>127412273</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>127412269</v>
       </c>
       <c r="B51" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>127412291</v>
       </c>
       <c r="B52" t="n">
-        <v>90141</v>
+        <v>90144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>127412250</v>
       </c>
       <c r="B53" t="n">
-        <v>90141</v>
+        <v>90144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412304</v>
+        <v>127412241</v>
       </c>
       <c r="B54" t="n">
-        <v>92620</v>
+        <v>78781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659596</v>
+        <v>659677</v>
       </c>
       <c r="R54" t="n">
-        <v>7189785</v>
+        <v>7189813</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412280</v>
+        <v>127412268</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>79641</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659557</v>
+        <v>659696</v>
       </c>
       <c r="R55" t="n">
-        <v>7189710</v>
+        <v>7189717</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412279</v>
+        <v>127412243</v>
       </c>
       <c r="B56" t="n">
-        <v>92644</v>
+        <v>79641</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659576</v>
+        <v>659677</v>
       </c>
       <c r="R56" t="n">
-        <v>7189699</v>
+        <v>7189813</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B57" t="n">
-        <v>92644</v>
+        <v>92623</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R57" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412241</v>
+        <v>127412280</v>
       </c>
       <c r="B58" t="n">
-        <v>78778</v>
+        <v>92623</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659557</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189710</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412268</v>
+        <v>127412293</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>78782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659696</v>
+        <v>659520</v>
       </c>
       <c r="R59" t="n">
-        <v>7189717</v>
+        <v>7189812</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412243</v>
+        <v>127412279</v>
       </c>
       <c r="B60" t="n">
-        <v>79638</v>
+        <v>92647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659677</v>
+        <v>659576</v>
       </c>
       <c r="R60" t="n">
-        <v>7189813</v>
+        <v>7189699</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412318</v>
       </c>
       <c r="B61" t="n">
-        <v>78779</v>
+        <v>92647</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659479</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189697</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7142,7 +7142,7 @@
         <v>127412272</v>
       </c>
       <c r="B62" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>127412299</v>
       </c>
       <c r="B63" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412286</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>79609</v>
+        <v>92625</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189705</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412267</v>
+        <v>127412312</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>92625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659676</v>
+        <v>659563</v>
       </c>
       <c r="R65" t="n">
-        <v>7189721</v>
+        <v>7189659</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412270</v>
+        <v>127412286</v>
       </c>
       <c r="B66" t="n">
-        <v>78779</v>
+        <v>79612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R66" t="n">
-        <v>7189717</v>
+        <v>7189705</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412317</v>
+        <v>127412267</v>
       </c>
       <c r="B67" t="n">
-        <v>92644</v>
+        <v>79612</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7680,21 +7680,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659491</v>
+        <v>659676</v>
       </c>
       <c r="R67" t="n">
-        <v>7189693</v>
+        <v>7189721</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412316</v>
+        <v>127412270</v>
       </c>
       <c r="B68" t="n">
-        <v>92644</v>
+        <v>78782</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659527</v>
+        <v>659696</v>
       </c>
       <c r="R68" t="n">
-        <v>7189674</v>
+        <v>7189717</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412265</v>
+        <v>127412317</v>
       </c>
       <c r="B69" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659682</v>
+        <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189733</v>
+        <v>7189693</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412245</v>
+        <v>127412316</v>
       </c>
       <c r="B70" t="n">
-        <v>92622</v>
+        <v>92647</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659677</v>
+        <v>659527</v>
       </c>
       <c r="R70" t="n">
-        <v>7189799</v>
+        <v>7189674</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412312</v>
+        <v>127412265</v>
       </c>
       <c r="B71" t="n">
-        <v>92622</v>
+        <v>92647</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659563</v>
+        <v>659682</v>
       </c>
       <c r="R71" t="n">
-        <v>7189659</v>
+        <v>7189733</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8202,7 +8202,7 @@
         <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412252</v>
+        <v>127412285</v>
       </c>
       <c r="B73" t="n">
-        <v>90141</v>
+        <v>78781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659674</v>
+        <v>659491</v>
       </c>
       <c r="R73" t="n">
-        <v>7189772</v>
+        <v>7189705</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412253</v>
+        <v>127412252</v>
       </c>
       <c r="B74" t="n">
-        <v>92628</v>
+        <v>90144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659620</v>
+        <v>659674</v>
       </c>
       <c r="R74" t="n">
-        <v>7189750</v>
+        <v>7189772</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412253</v>
       </c>
       <c r="B75" t="n">
-        <v>78778</v>
+        <v>92631</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659620</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189750</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8626,7 +8626,7 @@
         <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>92644</v>
+        <v>78690</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R77" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412276</v>
+        <v>127412254</v>
       </c>
       <c r="B78" t="n">
-        <v>78687</v>
+        <v>92647</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659721</v>
+        <v>659613</v>
       </c>
       <c r="R78" t="n">
-        <v>7189669</v>
+        <v>7189750</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412244</v>
+        <v>127412275</v>
       </c>
       <c r="B79" t="n">
-        <v>92640</v>
+        <v>79641</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659678</v>
+        <v>659650</v>
       </c>
       <c r="R79" t="n">
-        <v>7189811</v>
+        <v>7189690</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412275</v>
+        <v>127412244</v>
       </c>
       <c r="B80" t="n">
-        <v>79638</v>
+        <v>92643</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659650</v>
+        <v>659678</v>
       </c>
       <c r="R80" t="n">
-        <v>7189690</v>
+        <v>7189811</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B81" t="n">
-        <v>92620</v>
+        <v>78781</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R81" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B82" t="n">
-        <v>78778</v>
+        <v>92623</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R82" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9368,7 +9368,7 @@
         <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>127412296</v>
       </c>
       <c r="B84" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412240</v>
+        <v>127412287</v>
       </c>
       <c r="B87" t="n">
-        <v>92632</v>
+        <v>78781</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659675</v>
+        <v>659455</v>
       </c>
       <c r="R87" t="n">
-        <v>7189819</v>
+        <v>7189725</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412307</v>
+        <v>127412283</v>
       </c>
       <c r="B88" t="n">
-        <v>92620</v>
+        <v>78781</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659574</v>
+        <v>659523</v>
       </c>
       <c r="R88" t="n">
-        <v>7189797</v>
+        <v>7189683</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412310</v>
+        <v>127412240</v>
       </c>
       <c r="B89" t="n">
-        <v>92620</v>
+        <v>92635</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659559</v>
+        <v>659675</v>
       </c>
       <c r="R89" t="n">
-        <v>7189813</v>
+        <v>7189819</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412248</v>
+        <v>127412307</v>
       </c>
       <c r="B90" t="n">
-        <v>92656</v>
+        <v>92623</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659638</v>
+        <v>659574</v>
       </c>
       <c r="R90" t="n">
-        <v>7189786</v>
+        <v>7189797</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412287</v>
+        <v>127412310</v>
       </c>
       <c r="B91" t="n">
-        <v>78778</v>
+        <v>92623</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659455</v>
+        <v>659559</v>
       </c>
       <c r="R91" t="n">
-        <v>7189725</v>
+        <v>7189813</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412283</v>
+        <v>127412248</v>
       </c>
       <c r="B92" t="n">
-        <v>78778</v>
+        <v>92659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,21 +10330,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659523</v>
+        <v>659638</v>
       </c>
       <c r="R92" t="n">
-        <v>7189683</v>
+        <v>7189786</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10428,7 +10428,7 @@
         <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>127412303</v>
       </c>
       <c r="B94" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>127412257</v>
       </c>
       <c r="B95" t="n">
-        <v>92644</v>
+        <v>92647</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>127412302</v>
       </c>
       <c r="B96" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412260</v>
+        <v>127412274</v>
       </c>
       <c r="B20" t="n">
-        <v>92647</v>
+        <v>78788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659617</v>
+        <v>659657</v>
       </c>
       <c r="R20" t="n">
-        <v>7189732</v>
+        <v>7189693</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>78782</v>
+        <v>90152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B22" t="n">
-        <v>90144</v>
+        <v>92655</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R22" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3008,7 +3008,7 @@
         <v>127412282</v>
       </c>
       <c r="B23" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>127412277</v>
       </c>
       <c r="B24" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412256</v>
       </c>
       <c r="B28" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412258</v>
       </c>
       <c r="B31" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>127412295</v>
       </c>
       <c r="B32" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>90144</v>
+        <v>90152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>127412255</v>
       </c>
       <c r="B34" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>127412294</v>
       </c>
       <c r="B38" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412306</v>
       </c>
       <c r="B39" t="n">
-        <v>92643</v>
+        <v>92627</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659582</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189797</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B40" t="n">
-        <v>92619</v>
+        <v>92651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R40" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4916,7 +4916,7 @@
         <v>127412239</v>
       </c>
       <c r="B41" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>127412261</v>
       </c>
       <c r="B42" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>127412271</v>
       </c>
       <c r="B43" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>127412278</v>
       </c>
       <c r="B44" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>127412315</v>
       </c>
       <c r="B45" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>90144</v>
+        <v>90152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>127412273</v>
       </c>
       <c r="B50" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>127412269</v>
       </c>
       <c r="B51" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B52" t="n">
-        <v>90144</v>
+        <v>90152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R52" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B53" t="n">
-        <v>90144</v>
+        <v>90152</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R53" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412241</v>
+        <v>127412279</v>
       </c>
       <c r="B54" t="n">
-        <v>78781</v>
+        <v>92655</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659677</v>
+        <v>659576</v>
       </c>
       <c r="R54" t="n">
-        <v>7189813</v>
+        <v>7189699</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412268</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>79641</v>
+        <v>92655</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659696</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189717</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412243</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>79641</v>
+        <v>92631</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412304</v>
+        <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659596</v>
+        <v>659557</v>
       </c>
       <c r="R57" t="n">
-        <v>7189785</v>
+        <v>7189710</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412280</v>
+        <v>127412241</v>
       </c>
       <c r="B58" t="n">
-        <v>92623</v>
+        <v>78787</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659557</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189710</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412293</v>
+        <v>127412268</v>
       </c>
       <c r="B59" t="n">
-        <v>78782</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659520</v>
+        <v>659696</v>
       </c>
       <c r="R59" t="n">
-        <v>7189812</v>
+        <v>7189717</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412279</v>
+        <v>127412243</v>
       </c>
       <c r="B60" t="n">
-        <v>92647</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659576</v>
+        <v>659677</v>
       </c>
       <c r="R60" t="n">
-        <v>7189699</v>
+        <v>7189813</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412318</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>92647</v>
+        <v>78788</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659479</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189697</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7142,7 +7142,7 @@
         <v>127412272</v>
       </c>
       <c r="B62" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>127412299</v>
       </c>
       <c r="B63" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412317</v>
       </c>
       <c r="B64" t="n">
-        <v>92625</v>
+        <v>92655</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189693</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412312</v>
+        <v>127412316</v>
       </c>
       <c r="B65" t="n">
-        <v>92625</v>
+        <v>92655</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659563</v>
+        <v>659527</v>
       </c>
       <c r="R65" t="n">
-        <v>7189659</v>
+        <v>7189674</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412286</v>
+        <v>127412265</v>
       </c>
       <c r="B66" t="n">
-        <v>79612</v>
+        <v>92655</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659491</v>
+        <v>659682</v>
       </c>
       <c r="R66" t="n">
-        <v>7189705</v>
+        <v>7189733</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412267</v>
+        <v>127412245</v>
       </c>
       <c r="B67" t="n">
-        <v>79612</v>
+        <v>92633</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7680,21 +7680,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659676</v>
+        <v>659677</v>
       </c>
       <c r="R67" t="n">
-        <v>7189721</v>
+        <v>7189799</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412270</v>
+        <v>127412312</v>
       </c>
       <c r="B68" t="n">
-        <v>78782</v>
+        <v>92633</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659696</v>
+        <v>659563</v>
       </c>
       <c r="R68" t="n">
-        <v>7189717</v>
+        <v>7189659</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412317</v>
+        <v>127412270</v>
       </c>
       <c r="B69" t="n">
-        <v>92647</v>
+        <v>78788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R69" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412316</v>
+        <v>127412286</v>
       </c>
       <c r="B70" t="n">
-        <v>92647</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659527</v>
+        <v>659491</v>
       </c>
       <c r="R70" t="n">
-        <v>7189674</v>
+        <v>7189705</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412265</v>
+        <v>127412267</v>
       </c>
       <c r="B71" t="n">
-        <v>92647</v>
+        <v>79618</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659682</v>
+        <v>659676</v>
       </c>
       <c r="R71" t="n">
-        <v>7189733</v>
+        <v>7189721</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,10 +8199,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412262</v>
+        <v>127412242</v>
       </c>
       <c r="B72" t="n">
-        <v>92647</v>
+        <v>78788</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8210,21 +8210,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659670</v>
+        <v>659677</v>
       </c>
       <c r="R72" t="n">
-        <v>7189732</v>
+        <v>7189813</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412285</v>
+        <v>127412262</v>
       </c>
       <c r="B73" t="n">
-        <v>78781</v>
+        <v>92655</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659491</v>
+        <v>659670</v>
       </c>
       <c r="R73" t="n">
-        <v>7189705</v>
+        <v>7189732</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412252</v>
+        <v>127412253</v>
       </c>
       <c r="B74" t="n">
-        <v>90144</v>
+        <v>92639</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659674</v>
+        <v>659620</v>
       </c>
       <c r="R74" t="n">
-        <v>7189772</v>
+        <v>7189750</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412253</v>
+        <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659620</v>
+        <v>659491</v>
       </c>
       <c r="R75" t="n">
-        <v>7189750</v>
+        <v>7189705</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412242</v>
+        <v>127412252</v>
       </c>
       <c r="B76" t="n">
-        <v>78782</v>
+        <v>90152</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659677</v>
+        <v>659674</v>
       </c>
       <c r="R76" t="n">
-        <v>7189813</v>
+        <v>7189772</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,32 +8729,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412276</v>
+        <v>127412244</v>
       </c>
       <c r="B77" t="n">
-        <v>78690</v>
+        <v>92651</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659721</v>
+        <v>659678</v>
       </c>
       <c r="R77" t="n">
-        <v>7189669</v>
+        <v>7189811</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B78" t="n">
-        <v>92647</v>
+        <v>78696</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R78" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412275</v>
+        <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>79641</v>
+        <v>92655</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659650</v>
+        <v>659613</v>
       </c>
       <c r="R79" t="n">
-        <v>7189690</v>
+        <v>7189750</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412244</v>
+        <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>92643</v>
+        <v>79647</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659678</v>
+        <v>659650</v>
       </c>
       <c r="R80" t="n">
-        <v>7189811</v>
+        <v>7189690</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
         <v>127412289</v>
       </c>
       <c r="B81" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>127412313</v>
       </c>
       <c r="B82" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412296</v>
       </c>
       <c r="B83" t="n">
-        <v>78690</v>
+        <v>92633</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659476</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189791</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412296</v>
+        <v>127412266</v>
       </c>
       <c r="B84" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659476</v>
+        <v>659689</v>
       </c>
       <c r="R84" t="n">
-        <v>7189791</v>
+        <v>7189728</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412284</v>
       </c>
       <c r="B85" t="n">
-        <v>92625</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659491</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189705</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412284</v>
+        <v>127412308</v>
       </c>
       <c r="B86" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659491</v>
+        <v>659555</v>
       </c>
       <c r="R86" t="n">
-        <v>7189705</v>
+        <v>7189806</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412287</v>
+        <v>127412281</v>
       </c>
       <c r="B87" t="n">
-        <v>78781</v>
+        <v>78788</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659455</v>
+        <v>659533</v>
       </c>
       <c r="R87" t="n">
-        <v>7189725</v>
+        <v>7189693</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412283</v>
+        <v>127412248</v>
       </c>
       <c r="B88" t="n">
-        <v>78781</v>
+        <v>92667</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659523</v>
+        <v>659638</v>
       </c>
       <c r="R88" t="n">
-        <v>7189683</v>
+        <v>7189786</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10004,7 +10004,7 @@
         <v>127412240</v>
       </c>
       <c r="B89" t="n">
-        <v>92635</v>
+        <v>92643</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>127412307</v>
       </c>
       <c r="B90" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>127412310</v>
       </c>
       <c r="B91" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412248</v>
+        <v>127412287</v>
       </c>
       <c r="B92" t="n">
-        <v>92659</v>
+        <v>78787</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,21 +10330,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659638</v>
+        <v>659455</v>
       </c>
       <c r="R92" t="n">
-        <v>7189786</v>
+        <v>7189725</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B93" t="n">
-        <v>78782</v>
+        <v>78787</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R93" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412303</v>
+        <v>127412302</v>
       </c>
       <c r="B94" t="n">
-        <v>92647</v>
+        <v>92631</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659596</v>
+        <v>659609</v>
       </c>
       <c r="R94" t="n">
-        <v>7189785</v>
+        <v>7189804</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92647</v>
+        <v>92655</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B96" t="n">
-        <v>92623</v>
+        <v>92655</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R96" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90152</v>
+        <v>92656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412260</v>
+        <v>127412246</v>
       </c>
       <c r="B22" t="n">
-        <v>92655</v>
+        <v>90153</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659617</v>
+        <v>659647</v>
       </c>
       <c r="R22" t="n">
-        <v>7189732</v>
+        <v>7189793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3008,7 +3008,7 @@
         <v>127412282</v>
       </c>
       <c r="B23" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412277</v>
+        <v>127412292</v>
       </c>
       <c r="B24" t="n">
-        <v>92655</v>
+        <v>92634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,21 +3122,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659674</v>
+        <v>659492</v>
       </c>
       <c r="R24" t="n">
-        <v>7189662</v>
+        <v>7189757</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412292</v>
+        <v>127412277</v>
       </c>
       <c r="B25" t="n">
-        <v>92633</v>
+        <v>92656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659492</v>
+        <v>659674</v>
       </c>
       <c r="R25" t="n">
-        <v>7189757</v>
+        <v>7189662</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3326,7 +3326,7 @@
         <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412256</v>
       </c>
       <c r="B28" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412258</v>
       </c>
       <c r="B31" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412295</v>
+        <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>92652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659512</v>
+        <v>659629</v>
       </c>
       <c r="R32" t="n">
-        <v>7189786</v>
+        <v>7189751</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4068,7 +4068,7 @@
         <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>90152</v>
+        <v>90153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412255</v>
+        <v>127412295</v>
       </c>
       <c r="B34" t="n">
-        <v>92651</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659629</v>
+        <v>659512</v>
       </c>
       <c r="R34" t="n">
-        <v>7189751</v>
+        <v>7189786</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>78787</v>
+        <v>92628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R38" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>92627</v>
+        <v>92652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>92651</v>
+        <v>78787</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R40" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412261</v>
+        <v>127412271</v>
       </c>
       <c r="B42" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659600</v>
+        <v>659620</v>
       </c>
       <c r="R42" t="n">
-        <v>7189733</v>
+        <v>7189703</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412271</v>
+        <v>127412251</v>
       </c>
       <c r="B43" t="n">
-        <v>92655</v>
+        <v>92634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659620</v>
+        <v>659673</v>
       </c>
       <c r="R43" t="n">
-        <v>7189703</v>
+        <v>7189773</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5234,7 +5234,7 @@
         <v>127412278</v>
       </c>
       <c r="B44" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>127412315</v>
       </c>
       <c r="B45" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412251</v>
+        <v>127412261</v>
       </c>
       <c r="B46" t="n">
-        <v>92633</v>
+        <v>92656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659673</v>
+        <v>659600</v>
       </c>
       <c r="R46" t="n">
-        <v>7189773</v>
+        <v>7189733</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5552,7 +5552,7 @@
         <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>90152</v>
+        <v>90153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B52" t="n">
-        <v>90152</v>
+        <v>90153</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R52" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B53" t="n">
-        <v>90152</v>
+        <v>90153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R53" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412279</v>
+        <v>127412304</v>
       </c>
       <c r="B54" t="n">
-        <v>92655</v>
+        <v>92632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659576</v>
+        <v>659596</v>
       </c>
       <c r="R54" t="n">
-        <v>7189699</v>
+        <v>7189785</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412279</v>
       </c>
       <c r="B55" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659576</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189699</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412318</v>
       </c>
       <c r="B56" t="n">
-        <v>92631</v>
+        <v>92656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659479</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189697</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6612,7 +6612,7 @@
         <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412317</v>
+        <v>127412245</v>
       </c>
       <c r="B64" t="n">
-        <v>92655</v>
+        <v>92634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659677</v>
       </c>
       <c r="R64" t="n">
-        <v>7189693</v>
+        <v>7189799</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412316</v>
+        <v>127412317</v>
       </c>
       <c r="B65" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659527</v>
+        <v>659491</v>
       </c>
       <c r="R65" t="n">
-        <v>7189674</v>
+        <v>7189693</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412265</v>
+        <v>127412316</v>
       </c>
       <c r="B66" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659682</v>
+        <v>659527</v>
       </c>
       <c r="R66" t="n">
-        <v>7189733</v>
+        <v>7189674</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412245</v>
+        <v>127412312</v>
       </c>
       <c r="B67" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659677</v>
+        <v>659563</v>
       </c>
       <c r="R67" t="n">
-        <v>7189799</v>
+        <v>7189659</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412312</v>
+        <v>127412265</v>
       </c>
       <c r="B68" t="n">
-        <v>92633</v>
+        <v>92656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659563</v>
+        <v>659682</v>
       </c>
       <c r="R68" t="n">
-        <v>7189659</v>
+        <v>7189733</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8199,10 +8199,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412242</v>
+        <v>127412262</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>92656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8210,21 +8210,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659677</v>
+        <v>659670</v>
       </c>
       <c r="R72" t="n">
-        <v>7189813</v>
+        <v>7189732</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412262</v>
+        <v>127412253</v>
       </c>
       <c r="B73" t="n">
-        <v>92655</v>
+        <v>92640</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659670</v>
+        <v>659620</v>
       </c>
       <c r="R73" t="n">
-        <v>7189732</v>
+        <v>7189750</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412253</v>
+        <v>127412252</v>
       </c>
       <c r="B74" t="n">
-        <v>92639</v>
+        <v>90153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659620</v>
+        <v>659674</v>
       </c>
       <c r="R74" t="n">
-        <v>7189750</v>
+        <v>7189772</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B76" t="n">
-        <v>90152</v>
+        <v>78788</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R76" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,32 +8729,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412244</v>
+        <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>92651</v>
+        <v>78696</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659678</v>
+        <v>659721</v>
       </c>
       <c r="R77" t="n">
-        <v>7189811</v>
+        <v>7189669</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,32 +8835,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412276</v>
+        <v>127412244</v>
       </c>
       <c r="B78" t="n">
-        <v>78696</v>
+        <v>92652</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659721</v>
+        <v>659678</v>
       </c>
       <c r="R78" t="n">
-        <v>7189669</v>
+        <v>7189811</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8944,7 +8944,7 @@
         <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>127412313</v>
       </c>
       <c r="B82" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92633</v>
+        <v>78696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412266</v>
+        <v>127412284</v>
       </c>
       <c r="B84" t="n">
-        <v>92633</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659689</v>
+        <v>659491</v>
       </c>
       <c r="R84" t="n">
-        <v>7189728</v>
+        <v>7189705</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412284</v>
+        <v>127412296</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>92634</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659491</v>
+        <v>659476</v>
       </c>
       <c r="R85" t="n">
-        <v>7189705</v>
+        <v>7189791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412308</v>
+        <v>127412266</v>
       </c>
       <c r="B86" t="n">
-        <v>78696</v>
+        <v>92634</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659555</v>
+        <v>659689</v>
       </c>
       <c r="R86" t="n">
-        <v>7189806</v>
+        <v>7189728</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412281</v>
+        <v>127412240</v>
       </c>
       <c r="B87" t="n">
-        <v>78788</v>
+        <v>92644</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659533</v>
+        <v>659675</v>
       </c>
       <c r="R87" t="n">
-        <v>7189693</v>
+        <v>7189819</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412248</v>
+        <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>92667</v>
+        <v>92632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659638</v>
+        <v>659574</v>
       </c>
       <c r="R88" t="n">
-        <v>7189786</v>
+        <v>7189797</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412240</v>
+        <v>127412310</v>
       </c>
       <c r="B89" t="n">
-        <v>92643</v>
+        <v>92632</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659675</v>
+        <v>659559</v>
       </c>
       <c r="R89" t="n">
-        <v>7189819</v>
+        <v>7189813</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412307</v>
+        <v>127412287</v>
       </c>
       <c r="B90" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659574</v>
+        <v>659455</v>
       </c>
       <c r="R90" t="n">
-        <v>7189797</v>
+        <v>7189725</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412310</v>
+        <v>127412283</v>
       </c>
       <c r="B91" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659559</v>
+        <v>659523</v>
       </c>
       <c r="R91" t="n">
-        <v>7189813</v>
+        <v>7189683</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412287</v>
+        <v>127412248</v>
       </c>
       <c r="B92" t="n">
-        <v>78787</v>
+        <v>92668</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,21 +10330,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659455</v>
+        <v>659638</v>
       </c>
       <c r="R92" t="n">
-        <v>7189725</v>
+        <v>7189786</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412283</v>
+        <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659523</v>
+        <v>659533</v>
       </c>
       <c r="R93" t="n">
-        <v>7189683</v>
+        <v>7189693</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92631</v>
+        <v>92656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659680</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189752</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10640,7 +10640,7 @@
         <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92655</v>
+        <v>92656</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B96" t="n">
-        <v>92655</v>
+        <v>92632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412282</v>
+        <v>127412292</v>
       </c>
       <c r="B23" t="n">
-        <v>92656</v>
+        <v>92634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659532</v>
+        <v>659492</v>
       </c>
       <c r="R23" t="n">
-        <v>7189692</v>
+        <v>7189757</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412292</v>
+        <v>127412282</v>
       </c>
       <c r="B24" t="n">
-        <v>92634</v>
+        <v>92656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,21 +3122,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659492</v>
+        <v>659532</v>
       </c>
       <c r="R24" t="n">
-        <v>7189757</v>
+        <v>7189692</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B38" t="n">
-        <v>92628</v>
+        <v>92652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R38" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B39" t="n">
-        <v>92652</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412294</v>
+        <v>127412306</v>
       </c>
       <c r="B40" t="n">
-        <v>78787</v>
+        <v>92628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659520</v>
+        <v>659582</v>
       </c>
       <c r="R40" t="n">
-        <v>7189812</v>
+        <v>7189797</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412239</v>
+        <v>127412251</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>92634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659675</v>
+        <v>659673</v>
       </c>
       <c r="R41" t="n">
-        <v>7189819</v>
+        <v>7189773</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412271</v>
+        <v>127412301</v>
       </c>
       <c r="B42" t="n">
-        <v>92656</v>
+        <v>92632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R42" t="n">
-        <v>7189703</v>
+        <v>7189798</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412251</v>
+        <v>127412261</v>
       </c>
       <c r="B43" t="n">
-        <v>92634</v>
+        <v>92656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659673</v>
+        <v>659600</v>
       </c>
       <c r="R43" t="n">
-        <v>7189773</v>
+        <v>7189733</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412278</v>
+        <v>127412271</v>
       </c>
       <c r="B44" t="n">
         <v>92656</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659622</v>
+        <v>659620</v>
       </c>
       <c r="R44" t="n">
-        <v>7189650</v>
+        <v>7189703</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412315</v>
+        <v>127412278</v>
       </c>
       <c r="B45" t="n">
-        <v>90385</v>
+        <v>92656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659538</v>
+        <v>659622</v>
       </c>
       <c r="R45" t="n">
-        <v>7189669</v>
+        <v>7189650</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412261</v>
+        <v>127412315</v>
       </c>
       <c r="B46" t="n">
-        <v>92656</v>
+        <v>90385</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659600</v>
+        <v>659538</v>
       </c>
       <c r="R46" t="n">
-        <v>7189733</v>
+        <v>7189669</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412301</v>
+        <v>127412239</v>
       </c>
       <c r="B47" t="n">
-        <v>92632</v>
+        <v>78696</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659617</v>
+        <v>659675</v>
       </c>
       <c r="R47" t="n">
-        <v>7189798</v>
+        <v>7189819</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B52" t="n">
         <v>90153</v>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R52" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B53" t="n">
         <v>90153</v>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R53" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B55" t="n">
-        <v>92656</v>
+        <v>92632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R55" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412318</v>
+        <v>127412241</v>
       </c>
       <c r="B56" t="n">
-        <v>92656</v>
+        <v>78787</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659479</v>
+        <v>659677</v>
       </c>
       <c r="R56" t="n">
-        <v>7189697</v>
+        <v>7189813</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412280</v>
+        <v>127412268</v>
       </c>
       <c r="B57" t="n">
-        <v>92632</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659557</v>
+        <v>659696</v>
       </c>
       <c r="R57" t="n">
-        <v>7189710</v>
+        <v>7189717</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412241</v>
+        <v>127412243</v>
       </c>
       <c r="B58" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412268</v>
+        <v>127412279</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>92656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659696</v>
+        <v>659576</v>
       </c>
       <c r="R59" t="n">
-        <v>7189717</v>
+        <v>7189699</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412243</v>
+        <v>127412318</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>92656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659677</v>
+        <v>659479</v>
       </c>
       <c r="R60" t="n">
-        <v>7189813</v>
+        <v>7189697</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412245</v>
+        <v>127412317</v>
       </c>
       <c r="B64" t="n">
-        <v>92634</v>
+        <v>92656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189799</v>
+        <v>7189693</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412317</v>
+        <v>127412316</v>
       </c>
       <c r="B65" t="n">
         <v>92656</v>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659491</v>
+        <v>659527</v>
       </c>
       <c r="R65" t="n">
-        <v>7189693</v>
+        <v>7189674</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412316</v>
+        <v>127412265</v>
       </c>
       <c r="B66" t="n">
         <v>92656</v>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659527</v>
+        <v>659682</v>
       </c>
       <c r="R66" t="n">
-        <v>7189674</v>
+        <v>7189733</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412312</v>
+        <v>127412245</v>
       </c>
       <c r="B67" t="n">
         <v>92634</v>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659563</v>
+        <v>659677</v>
       </c>
       <c r="R67" t="n">
-        <v>7189659</v>
+        <v>7189799</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412265</v>
+        <v>127412312</v>
       </c>
       <c r="B68" t="n">
-        <v>92656</v>
+        <v>92634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659682</v>
+        <v>659563</v>
       </c>
       <c r="R68" t="n">
-        <v>7189733</v>
+        <v>7189659</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412270</v>
+        <v>127412286</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>79618</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189717</v>
+        <v>7189705</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412286</v>
+        <v>127412267</v>
       </c>
       <c r="B70" t="n">
         <v>79618</v>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659491</v>
+        <v>659676</v>
       </c>
       <c r="R70" t="n">
-        <v>7189705</v>
+        <v>7189721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412267</v>
+        <v>127412270</v>
       </c>
       <c r="B71" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659676</v>
+        <v>659696</v>
       </c>
       <c r="R71" t="n">
-        <v>7189721</v>
+        <v>7189717</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412262</v>
+        <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>92656</v>
+        <v>92640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659670</v>
+        <v>659620</v>
       </c>
       <c r="R72" t="n">
-        <v>7189732</v>
+        <v>7189750</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412253</v>
+        <v>127412252</v>
       </c>
       <c r="B73" t="n">
-        <v>92640</v>
+        <v>90153</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659620</v>
+        <v>659674</v>
       </c>
       <c r="R73" t="n">
-        <v>7189750</v>
+        <v>7189772</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B74" t="n">
-        <v>90153</v>
+        <v>78788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R74" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412262</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>92656</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659670</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189732</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412242</v>
+        <v>127412285</v>
       </c>
       <c r="B76" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,21 +8634,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659677</v>
+        <v>659491</v>
       </c>
       <c r="R76" t="n">
-        <v>7189813</v>
+        <v>7189705</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412276</v>
+        <v>127412275</v>
       </c>
       <c r="B77" t="n">
-        <v>78696</v>
+        <v>79647</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659721</v>
+        <v>659650</v>
       </c>
       <c r="R77" t="n">
-        <v>7189669</v>
+        <v>7189690</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,32 +8835,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412244</v>
+        <v>127412254</v>
       </c>
       <c r="B78" t="n">
-        <v>92652</v>
+        <v>92656</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659678</v>
+        <v>659613</v>
       </c>
       <c r="R78" t="n">
-        <v>7189811</v>
+        <v>7189750</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B79" t="n">
-        <v>92656</v>
+        <v>78696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R79" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412275</v>
+        <v>127412244</v>
       </c>
       <c r="B80" t="n">
-        <v>79647</v>
+        <v>92652</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659650</v>
+        <v>659678</v>
       </c>
       <c r="R80" t="n">
-        <v>7189690</v>
+        <v>7189811</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412289</v>
+        <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>92632</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +9164,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659530</v>
+        <v>659548</v>
       </c>
       <c r="R81" t="n">
-        <v>7189750</v>
+        <v>7189657</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412313</v>
+        <v>127412289</v>
       </c>
       <c r="B82" t="n">
-        <v>92632</v>
+        <v>78787</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,21 +9270,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659548</v>
+        <v>659530</v>
       </c>
       <c r="R82" t="n">
-        <v>7189657</v>
+        <v>7189750</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412296</v>
       </c>
       <c r="B83" t="n">
-        <v>78696</v>
+        <v>92634</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659476</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189791</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412284</v>
+        <v>127412266</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>92634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659491</v>
+        <v>659689</v>
       </c>
       <c r="R84" t="n">
-        <v>7189705</v>
+        <v>7189728</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B85" t="n">
-        <v>92634</v>
+        <v>78696</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R85" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412266</v>
+        <v>127412284</v>
       </c>
       <c r="B86" t="n">
-        <v>92634</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9694,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659689</v>
+        <v>659491</v>
       </c>
       <c r="R86" t="n">
-        <v>7189728</v>
+        <v>7189705</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412240</v>
+        <v>127412248</v>
       </c>
       <c r="B87" t="n">
-        <v>92644</v>
+        <v>92668</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659675</v>
+        <v>659638</v>
       </c>
       <c r="R87" t="n">
-        <v>7189819</v>
+        <v>7189786</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412307</v>
+        <v>127412287</v>
       </c>
       <c r="B88" t="n">
-        <v>92632</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659574</v>
+        <v>659455</v>
       </c>
       <c r="R88" t="n">
-        <v>7189797</v>
+        <v>7189725</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412310</v>
+        <v>127412283</v>
       </c>
       <c r="B89" t="n">
-        <v>92632</v>
+        <v>78787</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +10012,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659559</v>
+        <v>659523</v>
       </c>
       <c r="R89" t="n">
-        <v>7189813</v>
+        <v>7189683</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412287</v>
+        <v>127412307</v>
       </c>
       <c r="B90" t="n">
-        <v>78787</v>
+        <v>92632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659455</v>
+        <v>659574</v>
       </c>
       <c r="R90" t="n">
-        <v>7189725</v>
+        <v>7189797</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412283</v>
+        <v>127412310</v>
       </c>
       <c r="B91" t="n">
-        <v>78787</v>
+        <v>92632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659523</v>
+        <v>659559</v>
       </c>
       <c r="R91" t="n">
-        <v>7189683</v>
+        <v>7189813</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412248</v>
+        <v>127412240</v>
       </c>
       <c r="B92" t="n">
-        <v>92668</v>
+        <v>92644</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659638</v>
+        <v>659675</v>
       </c>
       <c r="R92" t="n">
-        <v>7189786</v>
+        <v>7189819</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10531,7 +10531,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412257</v>
+        <v>127412303</v>
       </c>
       <c r="B94" t="n">
         <v>92656</v>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659680</v>
+        <v>659596</v>
       </c>
       <c r="R94" t="n">
-        <v>7189752</v>
+        <v>7189785</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,7 +10637,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B95" t="n">
         <v>92656</v>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412274</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>92657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659657</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189693</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412274</v>
       </c>
       <c r="B21" t="n">
-        <v>92656</v>
+        <v>78788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2804,21 +2804,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659657</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189693</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>127412246</v>
       </c>
       <c r="B22" t="n">
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412292</v>
+        <v>127412277</v>
       </c>
       <c r="B23" t="n">
-        <v>92634</v>
+        <v>92657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,21 +3016,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659492</v>
+        <v>659674</v>
       </c>
       <c r="R23" t="n">
-        <v>7189757</v>
+        <v>7189662</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3114,7 +3114,7 @@
         <v>127412282</v>
       </c>
       <c r="B24" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412277</v>
+        <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92656</v>
+        <v>92635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659674</v>
+        <v>659492</v>
       </c>
       <c r="R25" t="n">
-        <v>7189662</v>
+        <v>7189757</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3326,7 +3326,7 @@
         <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412256</v>
+        <v>127412258</v>
       </c>
       <c r="B28" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659665</v>
+        <v>659663</v>
       </c>
       <c r="R28" t="n">
-        <v>7189754</v>
+        <v>7189743</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412309</v>
+        <v>127412305</v>
       </c>
       <c r="B29" t="n">
-        <v>90385</v>
+        <v>92657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659555</v>
+        <v>659567</v>
       </c>
       <c r="R29" t="n">
-        <v>7189806</v>
+        <v>7189783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B30" t="n">
-        <v>92656</v>
+        <v>90386</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R30" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412258</v>
+        <v>127412256</v>
       </c>
       <c r="B31" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659663</v>
+        <v>659665</v>
       </c>
       <c r="R31" t="n">
-        <v>7189743</v>
+        <v>7189754</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3962,7 +3962,7 @@
         <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>127412247</v>
       </c>
       <c r="B33" t="n">
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412300</v>
+        <v>127412288</v>
       </c>
       <c r="B36" t="n">
-        <v>92656</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,21 +4394,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659617</v>
+        <v>659455</v>
       </c>
       <c r="R36" t="n">
-        <v>7189798</v>
+        <v>7189725</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412288</v>
+        <v>127412300</v>
       </c>
       <c r="B37" t="n">
-        <v>79647</v>
+        <v>92657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659455</v>
+        <v>659617</v>
       </c>
       <c r="R37" t="n">
-        <v>7189725</v>
+        <v>7189798</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412297</v>
+        <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>92652</v>
+        <v>92629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659438</v>
+        <v>659582</v>
       </c>
       <c r="R38" t="n">
-        <v>7189796</v>
+        <v>7189797</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412306</v>
+        <v>127412297</v>
       </c>
       <c r="B40" t="n">
-        <v>92628</v>
+        <v>92653</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659582</v>
+        <v>659438</v>
       </c>
       <c r="R40" t="n">
-        <v>7189797</v>
+        <v>7189796</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412251</v>
+        <v>127412239</v>
       </c>
       <c r="B41" t="n">
-        <v>92634</v>
+        <v>78696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659673</v>
+        <v>659675</v>
       </c>
       <c r="R41" t="n">
-        <v>7189773</v>
+        <v>7189819</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412301</v>
+        <v>127412315</v>
       </c>
       <c r="B42" t="n">
-        <v>92632</v>
+        <v>90386</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659617</v>
+        <v>659538</v>
       </c>
       <c r="R42" t="n">
-        <v>7189798</v>
+        <v>7189669</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412261</v>
+        <v>127412271</v>
       </c>
       <c r="B43" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659600</v>
+        <v>659620</v>
       </c>
       <c r="R43" t="n">
-        <v>7189733</v>
+        <v>7189703</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412271</v>
+        <v>127412301</v>
       </c>
       <c r="B44" t="n">
-        <v>92656</v>
+        <v>92633</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R44" t="n">
-        <v>7189703</v>
+        <v>7189798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412278</v>
+        <v>127412261</v>
       </c>
       <c r="B45" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659622</v>
+        <v>659600</v>
       </c>
       <c r="R45" t="n">
-        <v>7189650</v>
+        <v>7189733</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412315</v>
+        <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>90385</v>
+        <v>92635</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659538</v>
+        <v>659673</v>
       </c>
       <c r="R46" t="n">
-        <v>7189669</v>
+        <v>7189773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412239</v>
+        <v>127412278</v>
       </c>
       <c r="B47" t="n">
-        <v>78696</v>
+        <v>92657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5560,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659675</v>
+        <v>659622</v>
       </c>
       <c r="R47" t="n">
-        <v>7189819</v>
+        <v>7189650</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5658,7 +5658,7 @@
         <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B52" t="n">
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R52" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B53" t="n">
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R53" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412304</v>
+        <v>127412293</v>
       </c>
       <c r="B54" t="n">
-        <v>92632</v>
+        <v>78788</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659596</v>
+        <v>659520</v>
       </c>
       <c r="R54" t="n">
-        <v>7189785</v>
+        <v>7189812</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412280</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>92632</v>
+        <v>92657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659557</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189710</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412241</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
-        <v>78787</v>
+        <v>92633</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412268</v>
+        <v>127412279</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>92657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659696</v>
+        <v>659576</v>
       </c>
       <c r="R57" t="n">
-        <v>7189717</v>
+        <v>7189699</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412243</v>
+        <v>127412280</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>92633</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659557</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189710</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412279</v>
+        <v>127412241</v>
       </c>
       <c r="B59" t="n">
-        <v>92656</v>
+        <v>78787</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659576</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189699</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412318</v>
+        <v>127412268</v>
       </c>
       <c r="B60" t="n">
-        <v>92656</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659479</v>
+        <v>659696</v>
       </c>
       <c r="R60" t="n">
-        <v>7189697</v>
+        <v>7189717</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412243</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412317</v>
+        <v>127412316</v>
       </c>
       <c r="B64" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659527</v>
       </c>
       <c r="R64" t="n">
-        <v>7189693</v>
+        <v>7189674</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412316</v>
+        <v>127412265</v>
       </c>
       <c r="B65" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659527</v>
+        <v>659682</v>
       </c>
       <c r="R65" t="n">
-        <v>7189674</v>
+        <v>7189733</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412265</v>
+        <v>127412317</v>
       </c>
       <c r="B66" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659682</v>
+        <v>659491</v>
       </c>
       <c r="R66" t="n">
-        <v>7189733</v>
+        <v>7189693</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7672,7 +7672,7 @@
         <v>127412245</v>
       </c>
       <c r="B67" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>127412312</v>
       </c>
       <c r="B68" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8305,32 +8305,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412252</v>
+        <v>127412242</v>
       </c>
       <c r="B73" t="n">
-        <v>90153</v>
+        <v>78788</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659674</v>
+        <v>659677</v>
       </c>
       <c r="R73" t="n">
-        <v>7189772</v>
+        <v>7189813</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412242</v>
+        <v>127412262</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>92657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659677</v>
+        <v>659670</v>
       </c>
       <c r="R74" t="n">
-        <v>7189813</v>
+        <v>7189732</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412262</v>
+        <v>127412252</v>
       </c>
       <c r="B75" t="n">
-        <v>92656</v>
+        <v>90154</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659670</v>
+        <v>659674</v>
       </c>
       <c r="R75" t="n">
-        <v>7189732</v>
+        <v>7189772</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412275</v>
+        <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659650</v>
+        <v>659721</v>
       </c>
       <c r="R77" t="n">
-        <v>7189690</v>
+        <v>7189669</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8838,7 +8838,7 @@
         <v>127412254</v>
       </c>
       <c r="B78" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412276</v>
+        <v>127412244</v>
       </c>
       <c r="B79" t="n">
-        <v>78696</v>
+        <v>92653</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659721</v>
+        <v>659678</v>
       </c>
       <c r="R79" t="n">
-        <v>7189669</v>
+        <v>7189811</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9047,32 +9047,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412244</v>
+        <v>127412275</v>
       </c>
       <c r="B80" t="n">
-        <v>92652</v>
+        <v>79647</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659678</v>
+        <v>659650</v>
       </c>
       <c r="R80" t="n">
-        <v>7189811</v>
+        <v>7189690</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
         <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412296</v>
+        <v>127412308</v>
       </c>
       <c r="B83" t="n">
-        <v>92634</v>
+        <v>78696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9376,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659476</v>
+        <v>659555</v>
       </c>
       <c r="R83" t="n">
-        <v>7189791</v>
+        <v>7189806</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B84" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R84" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412308</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
-        <v>78696</v>
+        <v>92635</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659555</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189806</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412248</v>
+        <v>127412281</v>
       </c>
       <c r="B87" t="n">
-        <v>92668</v>
+        <v>78788</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659638</v>
+        <v>659533</v>
       </c>
       <c r="R87" t="n">
-        <v>7189786</v>
+        <v>7189693</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412287</v>
+        <v>127412310</v>
       </c>
       <c r="B88" t="n">
-        <v>78787</v>
+        <v>92633</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659455</v>
+        <v>659559</v>
       </c>
       <c r="R88" t="n">
-        <v>7189725</v>
+        <v>7189813</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +10001,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412283</v>
+        <v>127412307</v>
       </c>
       <c r="B89" t="n">
-        <v>78787</v>
+        <v>92633</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +10012,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659523</v>
+        <v>659574</v>
       </c>
       <c r="R89" t="n">
-        <v>7189683</v>
+        <v>7189797</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,32 +10107,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412307</v>
+        <v>127412240</v>
       </c>
       <c r="B90" t="n">
-        <v>92632</v>
+        <v>92645</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659574</v>
+        <v>659675</v>
       </c>
       <c r="R90" t="n">
-        <v>7189797</v>
+        <v>7189819</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412310</v>
+        <v>127412287</v>
       </c>
       <c r="B91" t="n">
-        <v>92632</v>
+        <v>78787</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659559</v>
+        <v>659455</v>
       </c>
       <c r="R91" t="n">
-        <v>7189813</v>
+        <v>7189725</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412240</v>
+        <v>127412248</v>
       </c>
       <c r="B92" t="n">
-        <v>92644</v>
+        <v>92669</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659675</v>
+        <v>659638</v>
       </c>
       <c r="R92" t="n">
-        <v>7189819</v>
+        <v>7189786</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R93" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92656</v>
+        <v>92657</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R94" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B95" t="n">
-        <v>92656</v>
+        <v>92633</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R95" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B96" t="n">
-        <v>92632</v>
+        <v>92657</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R96" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>90155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R21" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412246</v>
+        <v>127412274</v>
       </c>
       <c r="B22" t="n">
-        <v>90154</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659647</v>
+        <v>659657</v>
       </c>
       <c r="R22" t="n">
-        <v>7189793</v>
+        <v>7189693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3008,7 +3008,7 @@
         <v>127412277</v>
       </c>
       <c r="B23" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>127412282</v>
       </c>
       <c r="B24" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B25" t="n">
-        <v>92635</v>
+        <v>92654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R25" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B26" t="n">
-        <v>92653</v>
+        <v>92636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R26" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3432,7 +3432,7 @@
         <v>127412249</v>
       </c>
       <c r="B27" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127412258</v>
       </c>
       <c r="B28" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127412305</v>
       </c>
       <c r="B29" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>127412309</v>
       </c>
       <c r="B30" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>127412256</v>
       </c>
       <c r="B31" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>127412255</v>
       </c>
       <c r="B32" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412247</v>
+        <v>127412295</v>
       </c>
       <c r="B33" t="n">
-        <v>90154</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659638</v>
+        <v>659512</v>
       </c>
       <c r="R33" t="n">
-        <v>7189791</v>
+        <v>7189786</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,32 +4171,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412295</v>
+        <v>127412247</v>
       </c>
       <c r="B34" t="n">
-        <v>78787</v>
+        <v>90155</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659512</v>
+        <v>659638</v>
       </c>
       <c r="R34" t="n">
-        <v>7189786</v>
+        <v>7189791</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4280,7 +4280,7 @@
         <v>127412290</v>
       </c>
       <c r="B35" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412288</v>
+        <v>127412300</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>92658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,21 +4394,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659455</v>
+        <v>659617</v>
       </c>
       <c r="R36" t="n">
-        <v>7189725</v>
+        <v>7189798</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412300</v>
+        <v>127412288</v>
       </c>
       <c r="B37" t="n">
-        <v>92657</v>
+        <v>79647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659617</v>
+        <v>659455</v>
       </c>
       <c r="R37" t="n">
-        <v>7189798</v>
+        <v>7189725</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
         <v>127412306</v>
       </c>
       <c r="B38" t="n">
-        <v>92629</v>
+        <v>92630</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B39" t="n">
-        <v>78787</v>
+        <v>92654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R39" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B40" t="n">
-        <v>92653</v>
+        <v>78787</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R40" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5022,7 +5022,7 @@
         <v>127412315</v>
       </c>
       <c r="B42" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>127412271</v>
       </c>
       <c r="B43" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>127412301</v>
       </c>
       <c r="B44" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>127412261</v>
       </c>
       <c r="B45" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>127412251</v>
       </c>
       <c r="B46" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>127412278</v>
       </c>
       <c r="B47" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>90154</v>
+        <v>90155</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>127412298</v>
       </c>
       <c r="B49" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B52" t="n">
-        <v>90154</v>
+        <v>90155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R52" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B53" t="n">
-        <v>90154</v>
+        <v>90155</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R53" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412293</v>
+        <v>127412318</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>92658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659520</v>
+        <v>659479</v>
       </c>
       <c r="R54" t="n">
-        <v>7189812</v>
+        <v>7189697</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>127412304</v>
       </c>
       <c r="B55" t="n">
-        <v>92657</v>
+        <v>92634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659596</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189785</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>127412279</v>
       </c>
       <c r="B56" t="n">
-        <v>92633</v>
+        <v>92658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659576</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189699</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B57" t="n">
-        <v>92657</v>
+        <v>92634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R57" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412280</v>
+        <v>127412241</v>
       </c>
       <c r="B58" t="n">
-        <v>92633</v>
+        <v>78787</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659557</v>
+        <v>659677</v>
       </c>
       <c r="R58" t="n">
-        <v>7189710</v>
+        <v>7189813</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412241</v>
+        <v>127412268</v>
       </c>
       <c r="B59" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659696</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189717</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412268</v>
+        <v>127412243</v>
       </c>
       <c r="B60" t="n">
         <v>79647</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R60" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412243</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>79647</v>
+        <v>78788</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412316</v>
+        <v>127412286</v>
       </c>
       <c r="B64" t="n">
-        <v>92657</v>
+        <v>79618</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659527</v>
+        <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189674</v>
+        <v>7189705</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412265</v>
+        <v>127412267</v>
       </c>
       <c r="B65" t="n">
-        <v>92657</v>
+        <v>79618</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659682</v>
+        <v>659676</v>
       </c>
       <c r="R65" t="n">
-        <v>7189733</v>
+        <v>7189721</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412317</v>
+        <v>127412270</v>
       </c>
       <c r="B66" t="n">
-        <v>92657</v>
+        <v>78788</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R66" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7672,7 +7672,7 @@
         <v>127412245</v>
       </c>
       <c r="B67" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>127412312</v>
       </c>
       <c r="B68" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412286</v>
+        <v>127412316</v>
       </c>
       <c r="B69" t="n">
-        <v>79618</v>
+        <v>92658</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659491</v>
+        <v>659527</v>
       </c>
       <c r="R69" t="n">
-        <v>7189705</v>
+        <v>7189674</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412267</v>
+        <v>127412265</v>
       </c>
       <c r="B70" t="n">
-        <v>79618</v>
+        <v>92658</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659676</v>
+        <v>659682</v>
       </c>
       <c r="R70" t="n">
-        <v>7189721</v>
+        <v>7189733</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412270</v>
+        <v>127412317</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>92658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659696</v>
+        <v>659491</v>
       </c>
       <c r="R71" t="n">
-        <v>7189717</v>
+        <v>7189693</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8202,7 +8202,7 @@
         <v>127412253</v>
       </c>
       <c r="B72" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412242</v>
+        <v>127412262</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>92658</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659677</v>
+        <v>659670</v>
       </c>
       <c r="R73" t="n">
-        <v>7189813</v>
+        <v>7189732</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412262</v>
+        <v>127412242</v>
       </c>
       <c r="B74" t="n">
-        <v>92657</v>
+        <v>78788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659670</v>
+        <v>659677</v>
       </c>
       <c r="R74" t="n">
-        <v>7189732</v>
+        <v>7189813</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412252</v>
+        <v>127412285</v>
       </c>
       <c r="B75" t="n">
-        <v>90154</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659674</v>
+        <v>659491</v>
       </c>
       <c r="R75" t="n">
-        <v>7189772</v>
+        <v>7189705</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412285</v>
+        <v>127412252</v>
       </c>
       <c r="B76" t="n">
-        <v>78787</v>
+        <v>90155</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659491</v>
+        <v>659674</v>
       </c>
       <c r="R76" t="n">
-        <v>7189705</v>
+        <v>7189772</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412276</v>
+        <v>127412254</v>
       </c>
       <c r="B77" t="n">
-        <v>78696</v>
+        <v>92658</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659721</v>
+        <v>659613</v>
       </c>
       <c r="R77" t="n">
-        <v>7189669</v>
+        <v>7189750</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,32 +8835,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412254</v>
+        <v>127412244</v>
       </c>
       <c r="B78" t="n">
-        <v>92657</v>
+        <v>92654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659613</v>
+        <v>659678</v>
       </c>
       <c r="R78" t="n">
-        <v>7189750</v>
+        <v>7189811</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,32 +8941,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412244</v>
+        <v>127412276</v>
       </c>
       <c r="B79" t="n">
-        <v>92653</v>
+        <v>78696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659678</v>
+        <v>659721</v>
       </c>
       <c r="R79" t="n">
-        <v>7189811</v>
+        <v>7189669</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
         <v>127412313</v>
       </c>
       <c r="B81" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412296</v>
+        <v>127412266</v>
       </c>
       <c r="B84" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659476</v>
+        <v>659689</v>
       </c>
       <c r="R84" t="n">
-        <v>7189791</v>
+        <v>7189728</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B85" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9789,10 +9789,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412281</v>
+        <v>127412310</v>
       </c>
       <c r="B87" t="n">
-        <v>78788</v>
+        <v>92634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9800,21 +9800,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659533</v>
+        <v>659559</v>
       </c>
       <c r="R87" t="n">
-        <v>7189693</v>
+        <v>7189813</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412310</v>
+        <v>127412307</v>
       </c>
       <c r="B88" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659559</v>
+        <v>659574</v>
       </c>
       <c r="R88" t="n">
-        <v>7189813</v>
+        <v>7189797</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412307</v>
+        <v>127412240</v>
       </c>
       <c r="B89" t="n">
-        <v>92633</v>
+        <v>92646</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659574</v>
+        <v>659675</v>
       </c>
       <c r="R89" t="n">
-        <v>7189797</v>
+        <v>7189819</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,32 +10107,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412240</v>
+        <v>127412287</v>
       </c>
       <c r="B90" t="n">
-        <v>92645</v>
+        <v>78787</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659675</v>
+        <v>659455</v>
       </c>
       <c r="R90" t="n">
-        <v>7189819</v>
+        <v>7189725</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412287</v>
+        <v>127412248</v>
       </c>
       <c r="B91" t="n">
-        <v>78787</v>
+        <v>92670</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659455</v>
+        <v>659638</v>
       </c>
       <c r="R91" t="n">
-        <v>7189725</v>
+        <v>7189786</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412248</v>
+        <v>127412283</v>
       </c>
       <c r="B92" t="n">
-        <v>92669</v>
+        <v>78787</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,21 +10330,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659638</v>
+        <v>659523</v>
       </c>
       <c r="R92" t="n">
-        <v>7189786</v>
+        <v>7189683</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412283</v>
+        <v>127412281</v>
       </c>
       <c r="B93" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659523</v>
+        <v>659533</v>
       </c>
       <c r="R93" t="n">
-        <v>7189683</v>
+        <v>7189693</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10534,7 +10534,7 @@
         <v>127412257</v>
       </c>
       <c r="B94" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>127412302</v>
       </c>
       <c r="B95" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>127412303</v>
       </c>
       <c r="B96" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412260</v>
+        <v>127412274</v>
       </c>
       <c r="B20" t="n">
-        <v>92658</v>
+        <v>78788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659617</v>
+        <v>659657</v>
       </c>
       <c r="R20" t="n">
-        <v>7189732</v>
+        <v>7189693</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,32 +2793,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412246</v>
+        <v>127412260</v>
       </c>
       <c r="B21" t="n">
-        <v>90155</v>
+        <v>92658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659647</v>
+        <v>659617</v>
       </c>
       <c r="R21" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412274</v>
+        <v>127412246</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>90155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659657</v>
+        <v>659647</v>
       </c>
       <c r="R22" t="n">
-        <v>7189693</v>
+        <v>7189793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412277</v>
+        <v>127412282</v>
       </c>
       <c r="B23" t="n">
         <v>92658</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659674</v>
+        <v>659532</v>
       </c>
       <c r="R23" t="n">
-        <v>7189662</v>
+        <v>7189692</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412282</v>
+        <v>127412277</v>
       </c>
       <c r="B24" t="n">
         <v>92658</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659532</v>
+        <v>659674</v>
       </c>
       <c r="R24" t="n">
-        <v>7189692</v>
+        <v>7189662</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412319</v>
+        <v>127412292</v>
       </c>
       <c r="B25" t="n">
-        <v>92654</v>
+        <v>92636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659459</v>
+        <v>659492</v>
       </c>
       <c r="R25" t="n">
-        <v>7189700</v>
+        <v>7189757</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412292</v>
+        <v>127412319</v>
       </c>
       <c r="B26" t="n">
-        <v>92636</v>
+        <v>92654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659492</v>
+        <v>659459</v>
       </c>
       <c r="R26" t="n">
-        <v>7189757</v>
+        <v>7189700</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412258</v>
+        <v>127412256</v>
       </c>
       <c r="B28" t="n">
         <v>92658</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659663</v>
+        <v>659665</v>
       </c>
       <c r="R28" t="n">
-        <v>7189743</v>
+        <v>7189754</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412305</v>
+        <v>127412309</v>
       </c>
       <c r="B29" t="n">
-        <v>92658</v>
+        <v>90387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659567</v>
+        <v>659555</v>
       </c>
       <c r="R29" t="n">
-        <v>7189783</v>
+        <v>7189806</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412309</v>
+        <v>127412305</v>
       </c>
       <c r="B30" t="n">
-        <v>90387</v>
+        <v>92658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659555</v>
+        <v>659567</v>
       </c>
       <c r="R30" t="n">
-        <v>7189806</v>
+        <v>7189783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412256</v>
+        <v>127412258</v>
       </c>
       <c r="B31" t="n">
         <v>92658</v>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659665</v>
+        <v>659663</v>
       </c>
       <c r="R31" t="n">
-        <v>7189754</v>
+        <v>7189743</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4701,32 +4701,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412297</v>
+        <v>127412294</v>
       </c>
       <c r="B39" t="n">
-        <v>92654</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659438</v>
+        <v>659520</v>
       </c>
       <c r="R39" t="n">
-        <v>7189796</v>
+        <v>7189812</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412294</v>
+        <v>127412297</v>
       </c>
       <c r="B40" t="n">
-        <v>78787</v>
+        <v>92654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659520</v>
+        <v>659438</v>
       </c>
       <c r="R40" t="n">
-        <v>7189812</v>
+        <v>7189796</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412315</v>
+        <v>127412261</v>
       </c>
       <c r="B42" t="n">
-        <v>90387</v>
+        <v>92658</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659538</v>
+        <v>659600</v>
       </c>
       <c r="R42" t="n">
-        <v>7189669</v>
+        <v>7189733</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412301</v>
+        <v>127412278</v>
       </c>
       <c r="B44" t="n">
-        <v>92634</v>
+        <v>92658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659617</v>
+        <v>659622</v>
       </c>
       <c r="R44" t="n">
-        <v>7189798</v>
+        <v>7189650</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412261</v>
+        <v>127412315</v>
       </c>
       <c r="B45" t="n">
-        <v>92658</v>
+        <v>90387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659600</v>
+        <v>659538</v>
       </c>
       <c r="R45" t="n">
-        <v>7189733</v>
+        <v>7189669</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412278</v>
+        <v>127412259</v>
       </c>
       <c r="B47" t="n">
-        <v>92658</v>
+        <v>90155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659622</v>
+        <v>659620</v>
       </c>
       <c r="R47" t="n">
-        <v>7189650</v>
+        <v>7189736</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412259</v>
+        <v>127412301</v>
       </c>
       <c r="B48" t="n">
-        <v>90155</v>
+        <v>92634</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R48" t="n">
-        <v>7189736</v>
+        <v>7189798</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412250</v>
+        <v>127412291</v>
       </c>
       <c r="B52" t="n">
         <v>90155</v>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659644</v>
+        <v>659545</v>
       </c>
       <c r="R52" t="n">
-        <v>7189774</v>
+        <v>7189763</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412291</v>
+        <v>127412250</v>
       </c>
       <c r="B53" t="n">
         <v>90155</v>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659545</v>
+        <v>659644</v>
       </c>
       <c r="R53" t="n">
-        <v>7189763</v>
+        <v>7189774</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,7 +6291,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412318</v>
+        <v>127412279</v>
       </c>
       <c r="B54" t="n">
         <v>92658</v>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659479</v>
+        <v>659576</v>
       </c>
       <c r="R54" t="n">
-        <v>7189697</v>
+        <v>7189699</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412304</v>
+        <v>127412318</v>
       </c>
       <c r="B55" t="n">
-        <v>92634</v>
+        <v>92658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659596</v>
+        <v>659479</v>
       </c>
       <c r="R55" t="n">
-        <v>7189785</v>
+        <v>7189697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412279</v>
+        <v>127412280</v>
       </c>
       <c r="B56" t="n">
-        <v>92658</v>
+        <v>92634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659576</v>
+        <v>659557</v>
       </c>
       <c r="R56" t="n">
-        <v>7189699</v>
+        <v>7189710</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412280</v>
+        <v>127412293</v>
       </c>
       <c r="B57" t="n">
-        <v>92634</v>
+        <v>78788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659557</v>
+        <v>659520</v>
       </c>
       <c r="R57" t="n">
-        <v>7189710</v>
+        <v>7189812</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412241</v>
+        <v>127412304</v>
       </c>
       <c r="B58" t="n">
-        <v>78787</v>
+        <v>92634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659677</v>
+        <v>659596</v>
       </c>
       <c r="R58" t="n">
-        <v>7189813</v>
+        <v>7189785</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412268</v>
+        <v>127412241</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659696</v>
+        <v>659677</v>
       </c>
       <c r="R59" t="n">
-        <v>7189717</v>
+        <v>7189813</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412243</v>
+        <v>127412268</v>
       </c>
       <c r="B60" t="n">
         <v>79647</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659677</v>
+        <v>659696</v>
       </c>
       <c r="R60" t="n">
-        <v>7189813</v>
+        <v>7189717</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>127412243</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412286</v>
+        <v>127412317</v>
       </c>
       <c r="B64" t="n">
-        <v>79618</v>
+        <v>92658</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7393,7 +7393,7 @@
         <v>659491</v>
       </c>
       <c r="R64" t="n">
-        <v>7189705</v>
+        <v>7189693</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412267</v>
+        <v>127412316</v>
       </c>
       <c r="B65" t="n">
-        <v>79618</v>
+        <v>92658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659676</v>
+        <v>659527</v>
       </c>
       <c r="R65" t="n">
-        <v>7189721</v>
+        <v>7189674</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,10 +7563,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412270</v>
+        <v>127412265</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>92658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659696</v>
+        <v>659682</v>
       </c>
       <c r="R66" t="n">
-        <v>7189717</v>
+        <v>7189733</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412316</v>
+        <v>127412286</v>
       </c>
       <c r="B69" t="n">
-        <v>92658</v>
+        <v>79618</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659527</v>
+        <v>659491</v>
       </c>
       <c r="R69" t="n">
-        <v>7189674</v>
+        <v>7189705</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412265</v>
+        <v>127412267</v>
       </c>
       <c r="B70" t="n">
-        <v>92658</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659682</v>
+        <v>659676</v>
       </c>
       <c r="R70" t="n">
-        <v>7189733</v>
+        <v>7189721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,10 +8093,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412317</v>
+        <v>127412270</v>
       </c>
       <c r="B71" t="n">
-        <v>92658</v>
+        <v>78788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659491</v>
+        <v>659696</v>
       </c>
       <c r="R71" t="n">
-        <v>7189693</v>
+        <v>7189717</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +8199,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412253</v>
+        <v>127412242</v>
       </c>
       <c r="B72" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659620</v>
+        <v>659677</v>
       </c>
       <c r="R72" t="n">
-        <v>7189750</v>
+        <v>7189813</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8411,32 +8411,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412242</v>
+        <v>127412253</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659677</v>
+        <v>659620</v>
       </c>
       <c r="R74" t="n">
-        <v>7189813</v>
+        <v>7189750</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8517,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412285</v>
+        <v>127412252</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>90155</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6276</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659491</v>
+        <v>659674</v>
       </c>
       <c r="R75" t="n">
-        <v>7189705</v>
+        <v>7189772</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,32 +8623,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412252</v>
+        <v>127412285</v>
       </c>
       <c r="B76" t="n">
-        <v>90155</v>
+        <v>78787</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659674</v>
+        <v>659491</v>
       </c>
       <c r="R76" t="n">
-        <v>7189772</v>
+        <v>7189705</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412254</v>
+        <v>127412276</v>
       </c>
       <c r="B77" t="n">
-        <v>92658</v>
+        <v>78696</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659613</v>
+        <v>659721</v>
       </c>
       <c r="R77" t="n">
-        <v>7189750</v>
+        <v>7189669</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8941,10 +8941,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412276</v>
+        <v>127412254</v>
       </c>
       <c r="B79" t="n">
-        <v>78696</v>
+        <v>92658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8952,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659721</v>
+        <v>659613</v>
       </c>
       <c r="R79" t="n">
-        <v>7189669</v>
+        <v>7189750</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9471,7 +9471,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412266</v>
+        <v>127412296</v>
       </c>
       <c r="B84" t="n">
         <v>92636</v>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659689</v>
+        <v>659476</v>
       </c>
       <c r="R84" t="n">
-        <v>7189728</v>
+        <v>7189791</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412296</v>
+        <v>127412266</v>
       </c>
       <c r="B85" t="n">
         <v>92636</v>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659476</v>
+        <v>659689</v>
       </c>
       <c r="R85" t="n">
-        <v>7189791</v>
+        <v>7189728</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9789,32 +9789,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412310</v>
+        <v>127412240</v>
       </c>
       <c r="B87" t="n">
-        <v>92634</v>
+        <v>92646</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659559</v>
+        <v>659675</v>
       </c>
       <c r="R87" t="n">
-        <v>7189813</v>
+        <v>7189819</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10001,32 +10001,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412240</v>
+        <v>127412310</v>
       </c>
       <c r="B89" t="n">
-        <v>92646</v>
+        <v>92634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659675</v>
+        <v>659559</v>
       </c>
       <c r="R89" t="n">
-        <v>7189819</v>
+        <v>7189813</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412287</v>
+        <v>127412248</v>
       </c>
       <c r="B90" t="n">
-        <v>78787</v>
+        <v>92670</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659455</v>
+        <v>659638</v>
       </c>
       <c r="R90" t="n">
-        <v>7189725</v>
+        <v>7189786</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412248</v>
+        <v>127412281</v>
       </c>
       <c r="B91" t="n">
-        <v>92670</v>
+        <v>78788</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10224,21 +10224,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659638</v>
+        <v>659533</v>
       </c>
       <c r="R91" t="n">
-        <v>7189786</v>
+        <v>7189693</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412283</v>
+        <v>127412287</v>
       </c>
       <c r="B92" t="n">
         <v>78787</v>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659523</v>
+        <v>659455</v>
       </c>
       <c r="R92" t="n">
-        <v>7189683</v>
+        <v>7189725</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412281</v>
+        <v>127412283</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659533</v>
+        <v>659523</v>
       </c>
       <c r="R93" t="n">
-        <v>7189693</v>
+        <v>7189683</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10531,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412257</v>
+        <v>127412302</v>
       </c>
       <c r="B94" t="n">
-        <v>92658</v>
+        <v>92634</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,21 +10542,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659680</v>
+        <v>659609</v>
       </c>
       <c r="R94" t="n">
-        <v>7189752</v>
+        <v>7189804</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412302</v>
+        <v>127412303</v>
       </c>
       <c r="B95" t="n">
-        <v>92634</v>
+        <v>92658</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10648,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659609</v>
+        <v>659596</v>
       </c>
       <c r="R95" t="n">
-        <v>7189804</v>
+        <v>7189785</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412303</v>
+        <v>127412257</v>
       </c>
       <c r="B96" t="n">
         <v>92658</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659596</v>
+        <v>659680</v>
       </c>
       <c r="R96" t="n">
-        <v>7189785</v>
+        <v>7189752</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -3959,32 +3959,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412255</v>
+        <v>127412295</v>
       </c>
       <c r="B32" t="n">
-        <v>92654</v>
+        <v>78787</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659629</v>
+        <v>659512</v>
       </c>
       <c r="R32" t="n">
-        <v>7189751</v>
+        <v>7189786</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +4065,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412295</v>
+        <v>127412255</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>92654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659512</v>
+        <v>659629</v>
       </c>
       <c r="R33" t="n">
-        <v>7189786</v>
+        <v>7189751</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412259</v>
+        <v>127412301</v>
       </c>
       <c r="B47" t="n">
-        <v>90155</v>
+        <v>92634</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659620</v>
+        <v>659617</v>
       </c>
       <c r="R47" t="n">
-        <v>7189736</v>
+        <v>7189798</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5655,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412301</v>
+        <v>127412259</v>
       </c>
       <c r="B48" t="n">
-        <v>92634</v>
+        <v>90155</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659617</v>
+        <v>659620</v>
       </c>
       <c r="R48" t="n">
-        <v>7189798</v>
+        <v>7189736</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412280</v>
+        <v>127412304</v>
       </c>
       <c r="B56" t="n">
         <v>92634</v>
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659557</v>
+        <v>659596</v>
       </c>
       <c r="R56" t="n">
-        <v>7189710</v>
+        <v>7189785</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412293</v>
+        <v>127412241</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6620,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659520</v>
+        <v>659677</v>
       </c>
       <c r="R57" t="n">
-        <v>7189812</v>
+        <v>7189813</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412304</v>
+        <v>127412268</v>
       </c>
       <c r="B58" t="n">
-        <v>92634</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,21 +6726,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659596</v>
+        <v>659696</v>
       </c>
       <c r="R58" t="n">
-        <v>7189785</v>
+        <v>7189717</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412241</v>
+        <v>127412243</v>
       </c>
       <c r="B59" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6927,10 +6927,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412268</v>
+        <v>127412280</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>92634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659696</v>
+        <v>659557</v>
       </c>
       <c r="R60" t="n">
-        <v>7189717</v>
+        <v>7189710</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412243</v>
+        <v>127412293</v>
       </c>
       <c r="B61" t="n">
-        <v>79647</v>
+        <v>78788</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659677</v>
+        <v>659520</v>
       </c>
       <c r="R61" t="n">
-        <v>7189813</v>
+        <v>7189812</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96482599</v>
+        <v>127412306</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659669.7552558185</v>
+        <v>659582</v>
       </c>
       <c r="R2" t="n">
-        <v>7189747.775702468</v>
+        <v>7189797</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +769,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96482594</v>
+        <v>127412239</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659676.9471048422</v>
+        <v>659675</v>
       </c>
       <c r="R3" t="n">
-        <v>7189725.09510189</v>
+        <v>7189819</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +875,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96482644</v>
+        <v>127412276</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659641.5396340394</v>
+        <v>659721</v>
       </c>
       <c r="R4" t="n">
-        <v>7189707.411271284</v>
+        <v>7189669</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +981,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96482593</v>
+        <v>127412308</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +1004,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659676.9471048422</v>
+        <v>659555</v>
       </c>
       <c r="R5" t="n">
-        <v>7189725.09510189</v>
+        <v>7189806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,22 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1087,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96482620</v>
+        <v>96482599</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659705.6744235059</v>
+        <v>659670</v>
       </c>
       <c r="R6" t="n">
-        <v>7189675.370589457</v>
+        <v>7189748</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,19 +1167,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96482646</v>
+        <v>96482602</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659676.158569468</v>
+        <v>659699</v>
       </c>
       <c r="R7" t="n">
-        <v>7189731.886635139</v>
+        <v>7189715</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1264,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96482631</v>
+        <v>96482603</v>
       </c>
       <c r="B8" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659665.6269949111</v>
+        <v>659681</v>
       </c>
       <c r="R8" t="n">
-        <v>7189744.993800859</v>
+        <v>7189692</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,19 +1361,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96482645</v>
+        <v>96482620</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659588.61161558</v>
+        <v>659706</v>
       </c>
       <c r="R9" t="n">
-        <v>7189778.058518362</v>
+        <v>7189676</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,19 +1458,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,50 +1487,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96482621</v>
+        <v>115285877</v>
       </c>
       <c r="B10" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659705.6744235059</v>
+        <v>659672</v>
       </c>
       <c r="R10" t="n">
-        <v>7189675.370589457</v>
+        <v>7189661</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,22 +1556,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96482630</v>
+        <v>127412309</v>
       </c>
       <c r="B11" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1604,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659584.2989903156</v>
+        <v>659555</v>
       </c>
       <c r="R11" t="n">
-        <v>7189786.798153022</v>
+        <v>7189806</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1753,22 +1662,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1687,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96482649</v>
+        <v>127412315</v>
       </c>
       <c r="B12" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1710,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659658.5126671516</v>
+        <v>659538</v>
       </c>
       <c r="R12" t="n">
-        <v>7189693.791936299</v>
+        <v>7189669</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,22 +1768,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,49 +1793,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96482648</v>
+        <v>96482630</v>
       </c>
       <c r="B13" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659683.0299885358</v>
+        <v>659584</v>
       </c>
       <c r="R13" t="n">
-        <v>7189723.282918984</v>
+        <v>7189787</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,19 +1873,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96482602</v>
+        <v>96482631</v>
       </c>
       <c r="B14" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659699.2824586094</v>
+        <v>659666</v>
       </c>
       <c r="R14" t="n">
-        <v>7189715.177781484</v>
+        <v>7189745</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,19 +1970,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,50 +1999,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96482603</v>
+        <v>127412249</v>
       </c>
       <c r="B15" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659680.4181403329</v>
+        <v>659615</v>
       </c>
       <c r="R15" t="n">
-        <v>7189691.966329859</v>
+        <v>7189777</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2201,22 +2068,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,49 +2093,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115285870</v>
+        <v>127412254</v>
       </c>
       <c r="B16" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2283,14 +2140,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>659491</v>
+        <v>659613</v>
       </c>
       <c r="R16" t="n">
-        <v>7189744</v>
+        <v>7189750</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,12 +2174,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2354,37 +2211,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115285871</v>
+        <v>127412256</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2394,14 +2246,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>659572</v>
+        <v>659665</v>
       </c>
       <c r="R17" t="n">
-        <v>7189663</v>
+        <v>7189754</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,12 +2280,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2465,15 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115285875</v>
+        <v>127412257</v>
       </c>
       <c r="B18" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2505,14 +2352,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>659667</v>
+        <v>659680</v>
       </c>
       <c r="R18" t="n">
-        <v>7189667</v>
+        <v>7189752</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2539,12 +2386,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2576,37 +2423,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115285877</v>
+        <v>127412258</v>
       </c>
       <c r="B19" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2616,14 +2458,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Mettjaur, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>659672</v>
+        <v>659663</v>
       </c>
       <c r="R19" t="n">
-        <v>7189661</v>
+        <v>7189743</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2650,12 +2492,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2687,32 +2529,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127412274</v>
+        <v>127412260</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2726,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659657</v>
+        <v>659617</v>
       </c>
       <c r="R20" t="n">
-        <v>7189693</v>
+        <v>7189732</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2793,14 +2635,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127412260</v>
+        <v>127412261</v>
       </c>
       <c r="B21" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2832,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659617</v>
+        <v>659600</v>
       </c>
       <c r="R21" t="n">
-        <v>7189732</v>
+        <v>7189733</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2899,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127412246</v>
+        <v>127412262</v>
       </c>
       <c r="B22" t="n">
-        <v>90155</v>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,21 +2752,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2938,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659647</v>
+        <v>659670</v>
       </c>
       <c r="R22" t="n">
-        <v>7189793</v>
+        <v>7189732</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3005,14 +2847,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127412282</v>
+        <v>127412265</v>
       </c>
       <c r="B23" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3044,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659532</v>
+        <v>659682</v>
       </c>
       <c r="R23" t="n">
-        <v>7189692</v>
+        <v>7189733</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3111,14 +2953,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127412277</v>
+        <v>127412271</v>
       </c>
       <c r="B24" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3150,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659674</v>
+        <v>659620</v>
       </c>
       <c r="R24" t="n">
-        <v>7189662</v>
+        <v>7189703</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,32 +3059,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127412292</v>
+        <v>127412277</v>
       </c>
       <c r="B25" t="n">
-        <v>92636</v>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659492</v>
+        <v>659674</v>
       </c>
       <c r="R25" t="n">
-        <v>7189757</v>
+        <v>7189662</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3323,32 +3165,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127412319</v>
+        <v>127412278</v>
       </c>
       <c r="B26" t="n">
-        <v>92654</v>
+        <v>93213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3362,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659459</v>
+        <v>659622</v>
       </c>
       <c r="R26" t="n">
-        <v>7189700</v>
+        <v>7189650</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3429,14 +3271,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127412249</v>
+        <v>127412279</v>
       </c>
       <c r="B27" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3468,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>659615</v>
+        <v>659576</v>
       </c>
       <c r="R27" t="n">
-        <v>7189777</v>
+        <v>7189699</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3535,14 +3377,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127412256</v>
+        <v>127412282</v>
       </c>
       <c r="B28" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3574,10 +3416,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659665</v>
+        <v>659532</v>
       </c>
       <c r="R28" t="n">
-        <v>7189754</v>
+        <v>7189692</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,32 +3483,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127412309</v>
+        <v>127412298</v>
       </c>
       <c r="B29" t="n">
-        <v>90387</v>
+        <v>93213</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3680,10 +3522,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659555</v>
+        <v>659428</v>
       </c>
       <c r="R29" t="n">
-        <v>7189806</v>
+        <v>7189801</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3747,14 +3589,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127412305</v>
+        <v>127412300</v>
       </c>
       <c r="B30" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3786,10 +3628,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659567</v>
+        <v>659617</v>
       </c>
       <c r="R30" t="n">
-        <v>7189783</v>
+        <v>7189798</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3853,14 +3695,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127412258</v>
+        <v>127412303</v>
       </c>
       <c r="B31" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3892,10 +3734,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659663</v>
+        <v>659596</v>
       </c>
       <c r="R31" t="n">
-        <v>7189743</v>
+        <v>7189785</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3959,32 +3801,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127412295</v>
+        <v>127412305</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>93213</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3998,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659512</v>
+        <v>659567</v>
       </c>
       <c r="R32" t="n">
-        <v>7189786</v>
+        <v>7189783</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4065,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127412255</v>
+        <v>127412311</v>
       </c>
       <c r="B33" t="n">
-        <v>92654</v>
+        <v>93213</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4104,10 +3946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659629</v>
+        <v>659536</v>
       </c>
       <c r="R33" t="n">
-        <v>7189751</v>
+        <v>7189824</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4171,10 +4013,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127412247</v>
+        <v>127412316</v>
       </c>
       <c r="B34" t="n">
-        <v>90155</v>
+        <v>93213</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4182,21 +4024,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4210,10 +4052,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659638</v>
+        <v>659527</v>
       </c>
       <c r="R34" t="n">
-        <v>7189791</v>
+        <v>7189674</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4277,32 +4119,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127412290</v>
+        <v>127412317</v>
       </c>
       <c r="B35" t="n">
-        <v>92636</v>
+        <v>93213</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4316,10 +4158,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>659545</v>
+        <v>659491</v>
       </c>
       <c r="R35" t="n">
-        <v>7189763</v>
+        <v>7189693</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4383,14 +4225,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127412300</v>
+        <v>127412318</v>
       </c>
       <c r="B36" t="n">
-        <v>92658</v>
+        <v>93213</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4422,10 +4264,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659617</v>
+        <v>659479</v>
       </c>
       <c r="R36" t="n">
-        <v>7189798</v>
+        <v>7189697</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,10 +4331,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127412288</v>
+        <v>115285871</v>
       </c>
       <c r="B37" t="n">
-        <v>79647</v>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4342,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4524,14 +4366,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659455</v>
+        <v>659572</v>
       </c>
       <c r="R37" t="n">
-        <v>7189725</v>
+        <v>7189663</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4558,12 +4400,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4595,32 +4437,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127412306</v>
+        <v>127412280</v>
       </c>
       <c r="B38" t="n">
-        <v>92630</v>
+        <v>93189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4634,10 +4476,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>659582</v>
+        <v>659557</v>
       </c>
       <c r="R38" t="n">
-        <v>7189797</v>
+        <v>7189710</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4701,10 +4543,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127412294</v>
+        <v>127412301</v>
       </c>
       <c r="B39" t="n">
-        <v>78787</v>
+        <v>93189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4712,21 +4554,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4740,10 +4582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659520</v>
+        <v>659617</v>
       </c>
       <c r="R39" t="n">
-        <v>7189812</v>
+        <v>7189798</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4807,32 +4649,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127412297</v>
+        <v>127412302</v>
       </c>
       <c r="B40" t="n">
-        <v>92654</v>
+        <v>93189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4846,10 +4688,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>659438</v>
+        <v>659609</v>
       </c>
       <c r="R40" t="n">
-        <v>7189796</v>
+        <v>7189804</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4913,10 +4755,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127412239</v>
+        <v>127412304</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>93189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4924,21 +4766,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4952,10 +4794,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>659675</v>
+        <v>659596</v>
       </c>
       <c r="R41" t="n">
-        <v>7189819</v>
+        <v>7189785</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5019,10 +4861,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127412261</v>
+        <v>127412307</v>
       </c>
       <c r="B42" t="n">
-        <v>92658</v>
+        <v>93189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,21 +4872,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5058,10 +4900,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659600</v>
+        <v>659574</v>
       </c>
       <c r="R42" t="n">
-        <v>7189733</v>
+        <v>7189797</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5125,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127412271</v>
+        <v>127412310</v>
       </c>
       <c r="B43" t="n">
-        <v>92658</v>
+        <v>93189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +4978,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5164,10 +5006,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659620</v>
+        <v>659559</v>
       </c>
       <c r="R43" t="n">
-        <v>7189703</v>
+        <v>7189813</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5231,10 +5073,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127412278</v>
+        <v>127412313</v>
       </c>
       <c r="B44" t="n">
-        <v>92658</v>
+        <v>93189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5242,21 +5084,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5270,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659622</v>
+        <v>659548</v>
       </c>
       <c r="R44" t="n">
-        <v>7189650</v>
+        <v>7189657</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5337,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127412315</v>
+        <v>96482648</v>
       </c>
       <c r="B45" t="n">
-        <v>90387</v>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,38 +5190,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>659538</v>
+        <v>659683</v>
       </c>
       <c r="R45" t="n">
-        <v>7189669</v>
+        <v>7189723</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5406,17 +5244,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5431,22 +5264,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127412251</v>
+        <v>96482649</v>
       </c>
       <c r="B46" t="n">
-        <v>92636</v>
+        <v>93191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5471,21 +5304,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>659673</v>
+        <v>659659</v>
       </c>
       <c r="R46" t="n">
-        <v>7189773</v>
+        <v>7189694</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5512,17 +5341,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5537,22 +5361,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127412301</v>
+        <v>127412245</v>
       </c>
       <c r="B47" t="n">
-        <v>92634</v>
+        <v>93191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5560,21 +5384,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5588,10 +5412,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>659617</v>
+        <v>659677</v>
       </c>
       <c r="R47" t="n">
-        <v>7189798</v>
+        <v>7189799</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5655,32 +5479,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127412259</v>
+        <v>127412251</v>
       </c>
       <c r="B48" t="n">
-        <v>90155</v>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5694,10 +5518,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>659620</v>
+        <v>659673</v>
       </c>
       <c r="R48" t="n">
-        <v>7189736</v>
+        <v>7189773</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5761,10 +5585,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127412298</v>
+        <v>127412266</v>
       </c>
       <c r="B49" t="n">
-        <v>92658</v>
+        <v>93191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5772,21 +5596,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5800,10 +5624,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>659428</v>
+        <v>659689</v>
       </c>
       <c r="R49" t="n">
-        <v>7189801</v>
+        <v>7189728</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5867,10 +5691,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127412273</v>
+        <v>127412290</v>
       </c>
       <c r="B50" t="n">
-        <v>79647</v>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5878,21 +5702,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5906,10 +5730,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>659657</v>
+        <v>659545</v>
       </c>
       <c r="R50" t="n">
-        <v>7189693</v>
+        <v>7189763</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5973,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127412269</v>
+        <v>127412292</v>
       </c>
       <c r="B51" t="n">
-        <v>78787</v>
+        <v>93191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,21 +5808,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6012,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>659696</v>
+        <v>659492</v>
       </c>
       <c r="R51" t="n">
-        <v>7189717</v>
+        <v>7189757</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6079,32 +5903,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127412291</v>
+        <v>127412296</v>
       </c>
       <c r="B52" t="n">
-        <v>90155</v>
+        <v>93191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6118,10 +5942,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>659545</v>
+        <v>659476</v>
       </c>
       <c r="R52" t="n">
-        <v>7189763</v>
+        <v>7189791</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6185,32 +6009,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127412250</v>
+        <v>127412312</v>
       </c>
       <c r="B53" t="n">
-        <v>90155</v>
+        <v>93191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6224,10 +6048,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659644</v>
+        <v>659563</v>
       </c>
       <c r="R53" t="n">
-        <v>7189774</v>
+        <v>7189659</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6291,10 +6115,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127412279</v>
+        <v>96482644</v>
       </c>
       <c r="B54" t="n">
-        <v>92658</v>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6302,38 +6126,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659576</v>
+        <v>659641</v>
       </c>
       <c r="R54" t="n">
-        <v>7189699</v>
+        <v>7189708</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6360,17 +6180,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6385,22 +6200,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127412318</v>
+        <v>96482645</v>
       </c>
       <c r="B55" t="n">
-        <v>92658</v>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6408,38 +6223,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>659479</v>
+        <v>659588</v>
       </c>
       <c r="R55" t="n">
-        <v>7189697</v>
+        <v>7189778</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6466,17 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6491,22 +6297,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127412304</v>
+        <v>96482646</v>
       </c>
       <c r="B56" t="n">
-        <v>92634</v>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,38 +6320,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>659596</v>
+        <v>659676</v>
       </c>
       <c r="R56" t="n">
-        <v>7189785</v>
+        <v>7189732</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6572,17 +6374,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6597,22 +6394,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127412241</v>
+        <v>127412253</v>
       </c>
       <c r="B57" t="n">
-        <v>78787</v>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6620,21 +6417,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6648,10 +6445,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>659677</v>
+        <v>659620</v>
       </c>
       <c r="R57" t="n">
-        <v>7189813</v>
+        <v>7189750</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6715,49 +6512,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127412268</v>
+        <v>96482621</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>93201</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>659696</v>
+        <v>659706</v>
       </c>
       <c r="R58" t="n">
-        <v>7189717</v>
+        <v>7189676</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6784,17 +6577,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6809,44 +6597,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127412243</v>
+        <v>115285875</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>93201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6856,14 +6644,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>659677</v>
+        <v>659667</v>
       </c>
       <c r="R59" t="n">
-        <v>7189813</v>
+        <v>7189667</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6890,12 +6678,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -6927,32 +6715,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127412280</v>
+        <v>127412240</v>
       </c>
       <c r="B60" t="n">
-        <v>92634</v>
+        <v>93201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6966,10 +6754,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>659557</v>
+        <v>659675</v>
       </c>
       <c r="R60" t="n">
-        <v>7189710</v>
+        <v>7189819</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7033,10 +6821,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127412293</v>
+        <v>115285870</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>93209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +6832,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7068,14 +6856,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Falträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>659520</v>
+        <v>659491</v>
       </c>
       <c r="R61" t="n">
-        <v>7189812</v>
+        <v>7189744</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7102,12 +6890,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7139,10 +6927,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127412272</v>
+        <v>127412244</v>
       </c>
       <c r="B62" t="n">
-        <v>79647</v>
+        <v>93209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,21 +6938,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7178,10 +6966,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>659634</v>
+        <v>659678</v>
       </c>
       <c r="R62" t="n">
-        <v>7189692</v>
+        <v>7189811</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7245,10 +7033,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127412299</v>
+        <v>127412255</v>
       </c>
       <c r="B63" t="n">
-        <v>78787</v>
+        <v>93209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,21 +7044,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7284,10 +7072,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>659637</v>
+        <v>659629</v>
       </c>
       <c r="R63" t="n">
-        <v>7189827</v>
+        <v>7189751</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7351,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127412317</v>
+        <v>127412297</v>
       </c>
       <c r="B64" t="n">
-        <v>92658</v>
+        <v>93209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7150,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7390,10 +7178,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>659491</v>
+        <v>659438</v>
       </c>
       <c r="R64" t="n">
-        <v>7189693</v>
+        <v>7189796</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7457,10 +7245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127412316</v>
+        <v>127412319</v>
       </c>
       <c r="B65" t="n">
-        <v>92658</v>
+        <v>93209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,21 +7256,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7496,10 +7284,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>659527</v>
+        <v>659459</v>
       </c>
       <c r="R65" t="n">
-        <v>7189674</v>
+        <v>7189700</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7563,49 +7351,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127412265</v>
+        <v>96482594</v>
       </c>
       <c r="B66" t="n">
-        <v>92658</v>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>659682</v>
+        <v>659677</v>
       </c>
       <c r="R66" t="n">
-        <v>7189733</v>
+        <v>7189725</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7632,17 +7416,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,44 +7436,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127412245</v>
+        <v>127412246</v>
       </c>
       <c r="B67" t="n">
-        <v>92636</v>
+        <v>90691</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7708,10 +7487,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>659677</v>
+        <v>659647</v>
       </c>
       <c r="R67" t="n">
-        <v>7189799</v>
+        <v>7189793</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7775,32 +7554,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127412312</v>
+        <v>127412247</v>
       </c>
       <c r="B68" t="n">
-        <v>92636</v>
+        <v>90691</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7814,10 +7593,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>659563</v>
+        <v>659638</v>
       </c>
       <c r="R68" t="n">
-        <v>7189659</v>
+        <v>7189791</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7881,32 +7660,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127412286</v>
+        <v>127412250</v>
       </c>
       <c r="B69" t="n">
-        <v>79618</v>
+        <v>90691</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6276</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7920,10 +7699,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>659491</v>
+        <v>659644</v>
       </c>
       <c r="R69" t="n">
-        <v>7189705</v>
+        <v>7189774</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7987,32 +7766,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127412267</v>
+        <v>127412252</v>
       </c>
       <c r="B70" t="n">
-        <v>79618</v>
+        <v>90691</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6276</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8026,10 +7805,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>659676</v>
+        <v>659674</v>
       </c>
       <c r="R70" t="n">
-        <v>7189721</v>
+        <v>7189772</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8093,32 +7872,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127412270</v>
+        <v>127412259</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>90691</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8132,10 +7911,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>659696</v>
+        <v>659620</v>
       </c>
       <c r="R71" t="n">
-        <v>7189717</v>
+        <v>7189736</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8199,32 +7978,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127412242</v>
+        <v>127412291</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>90691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8238,10 +8017,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>659677</v>
+        <v>659545</v>
       </c>
       <c r="R72" t="n">
-        <v>7189813</v>
+        <v>7189763</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8305,32 +8084,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127412262</v>
+        <v>127412284</v>
       </c>
       <c r="B73" t="n">
-        <v>92658</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8344,10 +8123,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>659670</v>
+        <v>659491</v>
       </c>
       <c r="R73" t="n">
-        <v>7189732</v>
+        <v>7189705</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8411,32 +8190,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127412253</v>
+        <v>127412241</v>
       </c>
       <c r="B74" t="n">
-        <v>92642</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8450,10 +8229,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>659620</v>
+        <v>659677</v>
       </c>
       <c r="R74" t="n">
-        <v>7189750</v>
+        <v>7189813</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8517,32 +8296,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127412252</v>
+        <v>127412269</v>
       </c>
       <c r="B75" t="n">
-        <v>90155</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8556,10 +8335,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>659674</v>
+        <v>659696</v>
       </c>
       <c r="R75" t="n">
-        <v>7189772</v>
+        <v>7189717</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8623,10 +8402,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127412285</v>
+        <v>127412283</v>
       </c>
       <c r="B76" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8662,10 +8441,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>659491</v>
+        <v>659523</v>
       </c>
       <c r="R76" t="n">
-        <v>7189705</v>
+        <v>7189683</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8729,10 +8508,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127412276</v>
+        <v>127412285</v>
       </c>
       <c r="B77" t="n">
-        <v>78696</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8740,21 +8519,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8768,10 +8547,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>659721</v>
+        <v>659491</v>
       </c>
       <c r="R77" t="n">
-        <v>7189669</v>
+        <v>7189705</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8835,32 +8614,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127412244</v>
+        <v>127412287</v>
       </c>
       <c r="B78" t="n">
-        <v>92654</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8874,10 +8653,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>659678</v>
+        <v>659455</v>
       </c>
       <c r="R78" t="n">
-        <v>7189811</v>
+        <v>7189725</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8941,10 +8720,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127412254</v>
+        <v>127412289</v>
       </c>
       <c r="B79" t="n">
-        <v>92658</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8952,21 +8731,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8980,7 +8759,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>659613</v>
+        <v>659530</v>
       </c>
       <c r="R79" t="n">
         <v>7189750</v>
@@ -9047,10 +8826,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127412275</v>
+        <v>127412294</v>
       </c>
       <c r="B80" t="n">
-        <v>79647</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9058,21 +8837,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9086,10 +8865,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>659650</v>
+        <v>659520</v>
       </c>
       <c r="R80" t="n">
-        <v>7189690</v>
+        <v>7189812</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9153,10 +8932,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127412313</v>
+        <v>127412295</v>
       </c>
       <c r="B81" t="n">
-        <v>92634</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9164,21 +8943,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9192,10 +8971,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>659548</v>
+        <v>659512</v>
       </c>
       <c r="R81" t="n">
-        <v>7189657</v>
+        <v>7189786</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9259,10 +9038,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127412289</v>
+        <v>127412299</v>
       </c>
       <c r="B82" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9298,10 +9077,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>659530</v>
+        <v>659637</v>
       </c>
       <c r="R82" t="n">
-        <v>7189750</v>
+        <v>7189827</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9365,10 +9144,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127412308</v>
+        <v>127412243</v>
       </c>
       <c r="B83" t="n">
-        <v>78696</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9376,21 +9155,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9404,10 +9183,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>659555</v>
+        <v>659677</v>
       </c>
       <c r="R83" t="n">
-        <v>7189806</v>
+        <v>7189813</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9471,10 +9250,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127412296</v>
+        <v>127412268</v>
       </c>
       <c r="B84" t="n">
-        <v>92636</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9482,21 +9261,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9510,10 +9289,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>659476</v>
+        <v>659696</v>
       </c>
       <c r="R84" t="n">
-        <v>7189791</v>
+        <v>7189717</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9577,10 +9356,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127412266</v>
+        <v>127412272</v>
       </c>
       <c r="B85" t="n">
-        <v>92636</v>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,21 +9367,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9616,10 +9395,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>659689</v>
+        <v>659634</v>
       </c>
       <c r="R85" t="n">
-        <v>7189728</v>
+        <v>7189692</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9683,10 +9462,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127412284</v>
+        <v>127412273</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9694,21 +9473,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9722,10 +9501,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>659491</v>
+        <v>659657</v>
       </c>
       <c r="R86" t="n">
-        <v>7189705</v>
+        <v>7189693</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9789,32 +9568,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127412240</v>
+        <v>127412275</v>
       </c>
       <c r="B87" t="n">
-        <v>92646</v>
+        <v>79946</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9828,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>659675</v>
+        <v>659650</v>
       </c>
       <c r="R87" t="n">
-        <v>7189819</v>
+        <v>7189690</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9895,10 +9674,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127412307</v>
+        <v>127412288</v>
       </c>
       <c r="B88" t="n">
-        <v>92634</v>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9906,21 +9685,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9934,10 +9713,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>659574</v>
+        <v>659455</v>
       </c>
       <c r="R88" t="n">
-        <v>7189797</v>
+        <v>7189725</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10001,10 +9780,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127412310</v>
+        <v>127412242</v>
       </c>
       <c r="B89" t="n">
-        <v>92634</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10012,21 +9791,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10040,7 +9819,7 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>659559</v>
+        <v>659677</v>
       </c>
       <c r="R89" t="n">
         <v>7189813</v>
@@ -10107,10 +9886,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127412248</v>
+        <v>127412270</v>
       </c>
       <c r="B90" t="n">
-        <v>92670</v>
+        <v>79085</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10118,21 +9897,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10146,10 +9925,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>659638</v>
+        <v>659696</v>
       </c>
       <c r="R90" t="n">
-        <v>7189786</v>
+        <v>7189717</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +9992,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127412281</v>
+        <v>127412274</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10252,7 +10031,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>659533</v>
+        <v>659657</v>
       </c>
       <c r="R91" t="n">
         <v>7189693</v>
@@ -10319,10 +10098,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127412287</v>
+        <v>127412281</v>
       </c>
       <c r="B92" t="n">
-        <v>78787</v>
+        <v>79085</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,21 +10109,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10358,10 +10137,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>659455</v>
+        <v>659533</v>
       </c>
       <c r="R92" t="n">
-        <v>7189725</v>
+        <v>7189693</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10425,10 +10204,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127412283</v>
+        <v>127412293</v>
       </c>
       <c r="B93" t="n">
-        <v>78787</v>
+        <v>79085</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,21 +10215,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10464,10 +10243,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>659523</v>
+        <v>659520</v>
       </c>
       <c r="R93" t="n">
-        <v>7189683</v>
+        <v>7189812</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10531,10 +10310,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127412302</v>
+        <v>96482593</v>
       </c>
       <c r="B94" t="n">
-        <v>92634</v>
+        <v>79917</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10542,38 +10321,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mettjaur, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>659609</v>
+        <v>659677</v>
       </c>
       <c r="R94" t="n">
-        <v>7189804</v>
+        <v>7189725</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10600,17 +10375,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10625,22 +10395,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Ingalill  Larsson, Carl Jansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127412303</v>
+        <v>127412267</v>
       </c>
       <c r="B95" t="n">
-        <v>92658</v>
+        <v>79917</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10648,21 +10418,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10676,10 +10446,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>659596</v>
+        <v>659676</v>
       </c>
       <c r="R95" t="n">
-        <v>7189785</v>
+        <v>7189721</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10743,10 +10513,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127412257</v>
+        <v>127412286</v>
       </c>
       <c r="B96" t="n">
-        <v>92658</v>
+        <v>79917</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10524,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10782,10 +10552,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>659680</v>
+        <v>659491</v>
       </c>
       <c r="R96" t="n">
-        <v>7189752</v>
+        <v>7189705</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>

--- a/artfynd/A 43734-2021 artfynd.xlsx
+++ b/artfynd/A 43734-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412306</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482602</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482603</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285877</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412315</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482630</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412249</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412254</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412256</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412257</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412258</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412260</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412261</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412262</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,6 +3060,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412265</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3056,6 +3171,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412271</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412277</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,6 +3393,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412278</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3374,6 +3504,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412279</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3480,6 +3615,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3586,6 +3726,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412298</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3692,6 +3837,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412300</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3798,6 +3948,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412303</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3904,6 +4059,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412305</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4010,6 +4170,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412311</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4116,6 +4281,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412316</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4222,6 +4392,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412317</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4328,6 +4503,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412318</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4434,6 +4614,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285871</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4540,6 +4725,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412280</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4646,6 +4836,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412301</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4752,6 +4947,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412302</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4858,6 +5058,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412304</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4964,6 +5169,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412307</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5070,6 +5280,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412310</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5176,6 +5391,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412313</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5273,6 +5493,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482648</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5370,6 +5595,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482649</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5476,6 +5706,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412245</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5582,6 +5817,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412251</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5688,6 +5928,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412266</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5794,6 +6039,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412290</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5900,6 +6150,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412292</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6006,6 +6261,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412296</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6112,6 +6372,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412312</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6209,6 +6474,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482644</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6306,6 +6576,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482645</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6403,6 +6678,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482646</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6509,6 +6789,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412253</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6606,6 +6891,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482621</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6712,6 +7002,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285875</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6818,6 +7113,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412240</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6924,6 +7224,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285870</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7030,6 +7335,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412244</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7136,6 +7446,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412255</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7242,6 +7557,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412297</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7348,6 +7668,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412319</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7445,6 +7770,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482594</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7551,6 +7881,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412246</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7657,6 +7992,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412247</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7763,6 +8103,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412250</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7869,6 +8214,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412252</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7975,6 +8325,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412259</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8081,6 +8436,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412291</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8187,6 +8547,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412284</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8293,6 +8658,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412241</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8399,6 +8769,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412269</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8505,6 +8880,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412283</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8611,6 +8991,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412285</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8717,6 +9102,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412287</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8823,6 +9213,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412289</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8929,6 +9324,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412294</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9035,6 +9435,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412295</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9141,6 +9546,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412299</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9247,6 +9657,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412243</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9353,6 +9768,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412268</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9459,6 +9879,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412272</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9565,6 +9990,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412273</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9671,6 +10101,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412275</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9777,6 +10212,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412288</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9883,6 +10323,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412242</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9989,6 +10434,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412270</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10095,6 +10545,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412274</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10201,6 +10656,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412281</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10307,6 +10767,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412293</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10404,6 +10869,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482593</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10510,6 +10980,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412267</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10616,8 +11091,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127412286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>